--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130142573</v>
+        <v>130142545</v>
       </c>
       <c r="B17" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,34 +2331,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467742</v>
+        <v>468004</v>
       </c>
       <c r="R17" t="n">
-        <v>7054804</v>
+        <v>7055356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2406,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>75 bålar på gammal grov gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,28 +2415,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130142512</v>
+        <v>130142541</v>
       </c>
       <c r="B18" t="n">
-        <v>78107</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,34 +2445,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467732</v>
+        <v>468161</v>
       </c>
       <c r="R18" t="n">
-        <v>7054900</v>
+        <v>7054893</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,7 +2520,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,6 +2529,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2524,7 +2548,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130142545</v>
+        <v>130142548</v>
       </c>
       <c r="B19" t="n">
         <v>79095</v>
@@ -2552,16 +2576,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2570,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468004</v>
+        <v>467726</v>
       </c>
       <c r="R19" t="n">
-        <v>7055356</v>
+        <v>7055026</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2610,7 +2625,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>75 bålar på gammal grov gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,7 +2653,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130142541</v>
+        <v>130142536</v>
       </c>
       <c r="B20" t="n">
         <v>79095</v>
@@ -2684,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468161</v>
+        <v>468265</v>
       </c>
       <c r="R20" t="n">
-        <v>7054893</v>
+        <v>7055202</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>50 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,7 +2767,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130142548</v>
+        <v>130130449</v>
       </c>
       <c r="B21" t="n">
         <v>79095</v>
@@ -2781,18 +2796,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467726</v>
+        <v>468106</v>
       </c>
       <c r="R21" t="n">
-        <v>7055026</v>
+        <v>7055256</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2822,14 +2835,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>200 bålar per gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,29 +2861,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130142536</v>
+        <v>130142512</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2868,45 +2890,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468265</v>
+        <v>467732</v>
       </c>
       <c r="R22" t="n">
-        <v>7055202</v>
+        <v>7054900</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2943,7 +2954,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,7 +2963,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2971,10 +2981,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130130449</v>
+        <v>130142573</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>91639</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,34 +2992,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468106</v>
+        <v>467742</v>
       </c>
       <c r="R23" t="n">
-        <v>7055256</v>
+        <v>7054804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,24 +3049,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>200 bålar per gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3071,12 +3071,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -5652,32 +5652,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130142504</v>
+        <v>130142509</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468112</v>
+        <v>467764</v>
       </c>
       <c r="R48" t="n">
-        <v>7055457</v>
+        <v>7055038</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På levande gammal grov gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5754,7 +5754,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130142534</v>
+        <v>130142504</v>
       </c>
       <c r="B49" t="n">
         <v>79095</v>
@@ -5783,18 +5783,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467764</v>
+        <v>468112</v>
       </c>
       <c r="R49" t="n">
-        <v>7054808</v>
+        <v>7055457</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5831,7 +5829,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På 200-årig gran i gammal granskog</t>
+          <t>På levande gammal grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5840,7 +5838,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5859,7 +5856,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130142528</v>
+        <v>130142534</v>
       </c>
       <c r="B50" t="n">
         <v>79095</v>
@@ -5887,16 +5884,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -5905,10 +5893,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467664</v>
+        <v>467764</v>
       </c>
       <c r="R50" t="n">
-        <v>7054936</v>
+        <v>7054808</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5945,7 +5933,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>400 bålar på gammal levande gran i gammal granskog</t>
+          <t>På 200-årig gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5973,7 +5961,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130142518</v>
+        <v>130142528</v>
       </c>
       <c r="B51" t="n">
         <v>79095</v>
@@ -6001,17 +5989,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468111</v>
+        <v>467664</v>
       </c>
       <c r="R51" t="n">
-        <v>7055166</v>
+        <v>7054936</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6048,7 +6047,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>400 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6057,6 +6056,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6075,7 +6075,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130130453</v>
+        <v>130142518</v>
       </c>
       <c r="B52" t="n">
         <v>79095</v>
@@ -6106,14 +6106,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468109</v>
+        <v>468111</v>
       </c>
       <c r="R52" t="n">
-        <v>7054902</v>
+        <v>7055166</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,24 +6143,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,57 +6165,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130142509</v>
+        <v>130130453</v>
       </c>
       <c r="B53" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467764</v>
+        <v>468109</v>
       </c>
       <c r="R53" t="n">
-        <v>7055038</v>
+        <v>7054902</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6255,14 +6245,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,12 +6277,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6918,56 +6918,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130142530</v>
+        <v>130142508</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468034</v>
+        <v>467673</v>
       </c>
       <c r="R60" t="n">
-        <v>7055454</v>
+        <v>7054942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7004,7 +6993,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7013,7 +7002,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7032,10 +7020,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130142542</v>
+        <v>130142576</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7043,45 +7031,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467980</v>
+        <v>467637</v>
       </c>
       <c r="R61" t="n">
-        <v>7055026</v>
+        <v>7054889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7118,7 +7100,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran (8 cm dbh) i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7127,67 +7109,63 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130142549</v>
+        <v>130142511</v>
       </c>
       <c r="B62" t="n">
-        <v>79095</v>
+        <v>80236</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467791</v>
+        <v>467765</v>
       </c>
       <c r="R62" t="n">
-        <v>7054826</v>
+        <v>7055022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7224,7 +7202,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7233,7 +7211,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7252,10 +7229,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130142576</v>
+        <v>130142530</v>
       </c>
       <c r="B63" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7263,39 +7240,45 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467637</v>
+        <v>468034</v>
       </c>
       <c r="R63" t="n">
-        <v>7054889</v>
+        <v>7055454</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7332,7 +7315,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7341,28 +7324,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130142517</v>
+        <v>130142542</v>
       </c>
       <c r="B64" t="n">
-        <v>56922</v>
+        <v>79095</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7370,38 +7354,45 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468271</v>
+        <v>467980</v>
       </c>
       <c r="R64" t="n">
-        <v>7054976</v>
+        <v>7055026</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7438,7 +7429,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>1 ex i gammal granskog</t>
+          <t>100 bålar på gammal levande gran (8 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7447,6 +7438,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7465,45 +7457,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130142511</v>
+        <v>130142549</v>
       </c>
       <c r="B65" t="n">
-        <v>80236</v>
+        <v>79095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467765</v>
+        <v>467791</v>
       </c>
       <c r="R65" t="n">
-        <v>7055022</v>
+        <v>7054826</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7540,7 +7535,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7549,6 +7544,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7567,45 +7563,49 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130142508</v>
+        <v>130142517</v>
       </c>
       <c r="B66" t="n">
-        <v>80229</v>
+        <v>56922</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467673</v>
+        <v>468271</v>
       </c>
       <c r="R66" t="n">
-        <v>7054942</v>
+        <v>7054976</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>1 ex i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130142545</v>
+        <v>130142573</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>91639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,45 +2331,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468004</v>
+        <v>467742</v>
       </c>
       <c r="R17" t="n">
-        <v>7055356</v>
+        <v>7054804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,7 +2395,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>75 bålar på gammal grov gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,29 +2404,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130142541</v>
+        <v>130142512</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,45 +2433,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468161</v>
+        <v>467732</v>
       </c>
       <c r="R18" t="n">
-        <v>7054893</v>
+        <v>7054900</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,7 +2497,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,7 +2506,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2548,7 +2524,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130142548</v>
+        <v>130142545</v>
       </c>
       <c r="B19" t="n">
         <v>79095</v>
@@ -2576,7 +2552,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2585,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467726</v>
+        <v>468004</v>
       </c>
       <c r="R19" t="n">
-        <v>7055026</v>
+        <v>7055356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2610,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>75 bålar på gammal grov gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,7 +2638,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130142536</v>
+        <v>130142541</v>
       </c>
       <c r="B20" t="n">
         <v>79095</v>
@@ -2699,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468265</v>
+        <v>468161</v>
       </c>
       <c r="R20" t="n">
-        <v>7055202</v>
+        <v>7054893</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2724,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,7 +2752,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130130449</v>
+        <v>130142548</v>
       </c>
       <c r="B21" t="n">
         <v>79095</v>
@@ -2796,16 +2781,18 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468106</v>
+        <v>467726</v>
       </c>
       <c r="R21" t="n">
-        <v>7055256</v>
+        <v>7055026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,24 +2822,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>200 bålar per gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2861,28 +2838,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130142512</v>
+        <v>130142536</v>
       </c>
       <c r="B22" t="n">
-        <v>78107</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,34 +2868,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467732</v>
+        <v>468265</v>
       </c>
       <c r="R22" t="n">
-        <v>7054900</v>
+        <v>7055202</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,7 +2943,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
+          <t>50 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,6 +2952,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2981,10 +2971,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130142573</v>
+        <v>130130449</v>
       </c>
       <c r="B23" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,34 +2982,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467742</v>
+        <v>468106</v>
       </c>
       <c r="R23" t="n">
-        <v>7054804</v>
+        <v>7055256</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3049,14 +3039,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>200 bålar per gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3071,57 +3071,59 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142581</v>
+        <v>130142531</v>
       </c>
       <c r="B24" t="n">
-        <v>92062</v>
+        <v>78107</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467806</v>
+        <v>467929</v>
       </c>
       <c r="R24" t="n">
-        <v>7054984</v>
+        <v>7055015</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3158,7 +3160,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,65 +3169,64 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130142524</v>
+        <v>130142581</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>92062</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468176</v>
+        <v>467806</v>
       </c>
       <c r="R25" t="n">
-        <v>7055315</v>
+        <v>7054984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,7 +3263,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,26 +3272,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130142514</v>
+        <v>130142524</v>
       </c>
       <c r="B26" t="n">
         <v>79095</v>
@@ -3319,16 +3319,18 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468321</v>
+        <v>468176</v>
       </c>
       <c r="R26" t="n">
-        <v>7055166</v>
+        <v>7055315</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3374,6 +3376,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3392,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130142531</v>
+        <v>130142514</v>
       </c>
       <c r="B27" t="n">
-        <v>78107</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,36 +3406,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467929</v>
+        <v>468321</v>
       </c>
       <c r="R27" t="n">
-        <v>7055015</v>
+        <v>7055166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,7 +3470,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3478,7 +3479,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -5652,32 +5652,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130142509</v>
+        <v>130142504</v>
       </c>
       <c r="B48" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467764</v>
+        <v>468112</v>
       </c>
       <c r="R48" t="n">
-        <v>7055038</v>
+        <v>7055457</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På levande gammal grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5754,7 +5754,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130142504</v>
+        <v>130142534</v>
       </c>
       <c r="B49" t="n">
         <v>79095</v>
@@ -5783,16 +5783,18 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468112</v>
+        <v>467764</v>
       </c>
       <c r="R49" t="n">
-        <v>7055457</v>
+        <v>7054808</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,7 +5831,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levande gammal grov gran i gammal granskog</t>
+          <t>På 200-årig gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5838,6 +5840,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5856,7 +5859,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130142534</v>
+        <v>130142528</v>
       </c>
       <c r="B50" t="n">
         <v>79095</v>
@@ -5884,7 +5887,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -5893,10 +5905,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467764</v>
+        <v>467664</v>
       </c>
       <c r="R50" t="n">
-        <v>7054808</v>
+        <v>7054936</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5933,7 +5945,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På 200-årig gran i gammal granskog</t>
+          <t>400 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5961,7 +5973,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130142528</v>
+        <v>130142518</v>
       </c>
       <c r="B51" t="n">
         <v>79095</v>
@@ -5989,28 +6001,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467664</v>
+        <v>468111</v>
       </c>
       <c r="R51" t="n">
-        <v>7054936</v>
+        <v>7055166</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6047,7 +6048,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>400 bålar på gammal levande gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6056,7 +6057,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6075,7 +6075,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130142518</v>
+        <v>130130453</v>
       </c>
       <c r="B52" t="n">
         <v>79095</v>
@@ -6106,14 +6106,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468111</v>
+        <v>468109</v>
       </c>
       <c r="R52" t="n">
-        <v>7055166</v>
+        <v>7054902</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,14 +6143,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6165,57 +6175,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130130453</v>
+        <v>130142509</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468109</v>
+        <v>467764</v>
       </c>
       <c r="R53" t="n">
-        <v>7054902</v>
+        <v>7055038</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6245,24 +6255,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,12 +6277,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>130142500</v>
       </c>
       <c r="B7" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1874,48 +1874,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130130446</v>
+        <v>130142539</v>
       </c>
       <c r="B13" t="n">
-        <v>92357</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467827</v>
+        <v>468233</v>
       </c>
       <c r="R13" t="n">
-        <v>7054966</v>
+        <v>7055007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,24 +1944,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Torraka av gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,40 +1964,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130130445</v>
+        <v>130142513</v>
       </c>
       <c r="B14" t="n">
-        <v>91659</v>
+        <v>83073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,30 +1990,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467790</v>
+        <v>468321</v>
       </c>
       <c r="R14" t="n">
-        <v>7054972</v>
+        <v>7055166</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,24 +2047,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Högstubbe, gran, med födosök från hackspett</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,22 +2069,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130142539</v>
+        <v>130130445</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,36 +2092,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468233</v>
+        <v>467790</v>
       </c>
       <c r="R15" t="n">
-        <v>7055007</v>
+        <v>7054972</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,14 +2145,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Högstubbe, gran, med födosök från hackspett</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,64 +2171,66 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130142513</v>
+        <v>130130446</v>
       </c>
       <c r="B16" t="n">
-        <v>83073</v>
+        <v>92359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468321</v>
+        <v>467827</v>
       </c>
       <c r="R16" t="n">
-        <v>7055166</v>
+        <v>7054966</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,14 +2260,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Torraka av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,18 +2286,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2323,7 +2323,7 @@
         <v>130142573</v>
       </c>
       <c r="B17" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130142512</v>
+        <v>130142545</v>
       </c>
       <c r="B18" t="n">
-        <v>78107</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,34 +2433,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467732</v>
+        <v>468004</v>
       </c>
       <c r="R18" t="n">
-        <v>7054900</v>
+        <v>7055356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,7 +2508,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
+          <t>75 bålar på gammal grov gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,6 +2517,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2524,7 +2536,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130142545</v>
+        <v>130142541</v>
       </c>
       <c r="B19" t="n">
         <v>79095</v>
@@ -2554,7 +2566,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2570,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468004</v>
+        <v>468161</v>
       </c>
       <c r="R19" t="n">
-        <v>7055356</v>
+        <v>7054893</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2610,7 +2622,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>75 bålar på gammal grov gran</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,7 +2650,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130142541</v>
+        <v>130142548</v>
       </c>
       <c r="B20" t="n">
         <v>79095</v>
@@ -2666,16 +2678,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2684,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468161</v>
+        <v>467726</v>
       </c>
       <c r="R20" t="n">
-        <v>7054893</v>
+        <v>7055026</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,7 +2727,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,7 +2755,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130142548</v>
+        <v>130142536</v>
       </c>
       <c r="B21" t="n">
         <v>79095</v>
@@ -2780,7 +2783,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2789,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467726</v>
+        <v>468265</v>
       </c>
       <c r="R21" t="n">
-        <v>7055026</v>
+        <v>7055202</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,7 +2841,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,7 +2869,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130142536</v>
+        <v>130130449</v>
       </c>
       <c r="B22" t="n">
         <v>79095</v>
@@ -2885,28 +2897,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468265</v>
+        <v>468106</v>
       </c>
       <c r="R22" t="n">
-        <v>7055202</v>
+        <v>7055256</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,14 +2937,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran i gammal granskog</t>
+          <t>200 bålar per gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,29 +2963,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130130449</v>
+        <v>130142512</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,34 +2992,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468106</v>
+        <v>467732</v>
       </c>
       <c r="R23" t="n">
-        <v>7055256</v>
+        <v>7054900</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,24 +3049,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>200 bålar per gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3071,22 +3071,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142531</v>
+        <v>130142524</v>
       </c>
       <c r="B24" t="n">
-        <v>78107</v>
+        <v>79095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,21 +3094,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467929</v>
+        <v>468176</v>
       </c>
       <c r="R24" t="n">
-        <v>7055015</v>
+        <v>7055315</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,32 +3188,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130142581</v>
+        <v>130142514</v>
       </c>
       <c r="B25" t="n">
-        <v>92062</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467806</v>
+        <v>468321</v>
       </c>
       <c r="R25" t="n">
-        <v>7054984</v>
+        <v>7055166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,22 +3278,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130142524</v>
+        <v>130142531</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468176</v>
+        <v>467929</v>
       </c>
       <c r="R26" t="n">
-        <v>7055315</v>
+        <v>7055015</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130142514</v>
+        <v>130142581</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>92064</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468321</v>
+        <v>467806</v>
       </c>
       <c r="R27" t="n">
-        <v>7055166</v>
+        <v>7054984</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,12 +3485,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
         <v>130142574</v>
       </c>
       <c r="B29" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>130142520</v>
       </c>
       <c r="B35" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>130142519</v>
       </c>
       <c r="B40" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130142501</v>
       </c>
       <c r="B47" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6075,45 +6075,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130130453</v>
+        <v>130142509</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468109</v>
+        <v>467764</v>
       </c>
       <c r="R52" t="n">
-        <v>7054902</v>
+        <v>7055038</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,24 +6143,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,57 +6165,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130142509</v>
+        <v>130130453</v>
       </c>
       <c r="B53" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467764</v>
+        <v>468109</v>
       </c>
       <c r="R53" t="n">
-        <v>7055038</v>
+        <v>7054902</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6255,14 +6245,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,12 +6277,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130142579</v>
+        <v>130142578</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6512,43 +6512,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467640</v>
+        <v>467794</v>
       </c>
       <c r="R56" t="n">
-        <v>7054887</v>
+        <v>7054821</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6585,7 +6576,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1000 ex på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6612,10 +6603,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130142578</v>
+        <v>130142579</v>
       </c>
       <c r="B57" t="n">
-        <v>78107</v>
+        <v>79095</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6623,34 +6614,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467794</v>
+        <v>467640</v>
       </c>
       <c r="R57" t="n">
-        <v>7054821</v>
+        <v>7054887</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1000 ex på gammal gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6918,45 +6918,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130142508</v>
+        <v>130142517</v>
       </c>
       <c r="B60" t="n">
-        <v>80229</v>
+        <v>56922</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467673</v>
+        <v>468271</v>
       </c>
       <c r="R60" t="n">
-        <v>7054942</v>
+        <v>7054976</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6993,7 +6997,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>1 ex i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7020,10 +7024,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130142576</v>
+        <v>130142530</v>
       </c>
       <c r="B61" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7031,39 +7035,45 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467637</v>
+        <v>468034</v>
       </c>
       <c r="R61" t="n">
-        <v>7054889</v>
+        <v>7055454</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7100,7 +7110,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7109,18 +7119,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7229,56 +7240,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130142530</v>
+        <v>130142508</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468034</v>
+        <v>467673</v>
       </c>
       <c r="R63" t="n">
-        <v>7055454</v>
+        <v>7054942</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7324,7 +7324,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7563,10 +7562,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130142517</v>
+        <v>130142576</v>
       </c>
       <c r="B66" t="n">
-        <v>56922</v>
+        <v>57741</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,16 +7573,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7591,9 +7590,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468271</v>
+        <v>467637</v>
       </c>
       <c r="R66" t="n">
-        <v>7054976</v>
+        <v>7054889</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>1 ex i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7657,12 +7657,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130142506</v>
+        <v>130142522</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,17 +703,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468050</v>
+        <v>468134</v>
       </c>
       <c r="R2" t="n">
-        <v>7055309</v>
+        <v>7054850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>100 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130142502</v>
+        <v>130142527</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,17 +814,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468068</v>
+        <v>468067</v>
       </c>
       <c r="R3" t="n">
-        <v>7055228</v>
+        <v>7055001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog</t>
+          <t>100 bålar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130142522</v>
+        <v>130142506</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,26 +928,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468134</v>
+        <v>468050</v>
       </c>
       <c r="R4" t="n">
-        <v>7054850</v>
+        <v>7055309</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +975,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130142527</v>
+        <v>130142502</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,28 +1030,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468067</v>
+        <v>468068</v>
       </c>
       <c r="R5" t="n">
-        <v>7055001</v>
+        <v>7055228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1077,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran</t>
+          <t>på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130142510</v>
+        <v>130142500</v>
       </c>
       <c r="B6" t="n">
-        <v>80201</v>
+        <v>91692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467764</v>
+        <v>468254</v>
       </c>
       <c r="R6" t="n">
-        <v>7055038</v>
+        <v>7054950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142500</v>
+        <v>130142510</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
+        <v>80286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468254</v>
+        <v>467764</v>
       </c>
       <c r="R7" t="n">
-        <v>7054950</v>
+        <v>7055038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,7 +1311,7 @@
         <v>130142540</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>130142526</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130142537</v>
+        <v>130142505</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,45 +1529,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467722</v>
+        <v>468112</v>
       </c>
       <c r="R10" t="n">
-        <v>7054932</v>
+        <v>7055457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1598,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran i gammal granskog</t>
+          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,7 +1607,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1632,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130142505</v>
+        <v>130142537</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,39 +1636,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468112</v>
+        <v>467722</v>
       </c>
       <c r="R11" t="n">
-        <v>7055457</v>
+        <v>7054932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1711,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
+          <t>100 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,6 +1720,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>130130450</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,47 +1874,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130142539</v>
+        <v>130130446</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>92446</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468233</v>
+        <v>467827</v>
       </c>
       <c r="R13" t="n">
-        <v>7055007</v>
+        <v>7054966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,14 +1945,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Torraka av gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,25 +1975,40 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130142513</v>
+        <v>130130445</v>
       </c>
       <c r="B14" t="n">
-        <v>83073</v>
+        <v>91748</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,34 +2016,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468321</v>
+        <v>467790</v>
       </c>
       <c r="R14" t="n">
-        <v>7055166</v>
+        <v>7054972</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,14 +2069,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Högstubbe, gran, med födosök från hackspett</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,22 +2101,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130130445</v>
+        <v>130142513</v>
       </c>
       <c r="B15" t="n">
-        <v>91661</v>
+        <v>83158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,30 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467790</v>
+        <v>468321</v>
       </c>
       <c r="R15" t="n">
-        <v>7054972</v>
+        <v>7055166</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,24 +2181,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Högstubbe, gran, med födosök från hackspett</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2177,60 +2203,59 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130130446</v>
+        <v>130142539</v>
       </c>
       <c r="B16" t="n">
-        <v>92359</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467827</v>
+        <v>468233</v>
       </c>
       <c r="R16" t="n">
-        <v>7054966</v>
+        <v>7055007</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,24 +2285,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Torraka av gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,30 +2305,15 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2323,7 +2323,7 @@
         <v>130142573</v>
       </c>
       <c r="B17" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>130142545</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>130142541</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130142548</v>
+        <v>130142536</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,7 +2678,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2687,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467726</v>
+        <v>468265</v>
       </c>
       <c r="R20" t="n">
-        <v>7055026</v>
+        <v>7055202</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,7 +2736,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2755,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130142536</v>
+        <v>130130449</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,28 +2792,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468265</v>
+        <v>468106</v>
       </c>
       <c r="R21" t="n">
-        <v>7055202</v>
+        <v>7055256</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,14 +2832,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran i gammal granskog</t>
+          <t>200 bålar per gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2850,29 +2858,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130130449</v>
+        <v>130142548</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,16 +2905,18 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468106</v>
+        <v>467726</v>
       </c>
       <c r="R22" t="n">
-        <v>7055256</v>
+        <v>7055026</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,24 +2946,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>200 bålar per gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,18 +2962,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2984,7 +2984,7 @@
         <v>130142512</v>
       </c>
       <c r="B23" t="n">
-        <v>78107</v>
+        <v>78192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,47 +3083,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142524</v>
+        <v>130142581</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>92151</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468176</v>
+        <v>467806</v>
       </c>
       <c r="R24" t="n">
-        <v>7055315</v>
+        <v>7054984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3158,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,29 +3167,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130142514</v>
+        <v>130142524</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,16 +3214,18 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468321</v>
+        <v>468176</v>
       </c>
       <c r="R25" t="n">
-        <v>7055166</v>
+        <v>7055315</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3262,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3272,6 +3271,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>130142531</v>
       </c>
       <c r="B26" t="n">
-        <v>78107</v>
+        <v>78192</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3395,32 +3395,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130142581</v>
+        <v>130142514</v>
       </c>
       <c r="B27" t="n">
-        <v>92064</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467806</v>
+        <v>468321</v>
       </c>
       <c r="R27" t="n">
-        <v>7054984</v>
+        <v>7055166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,44 +3485,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130142516</v>
+        <v>130142574</v>
       </c>
       <c r="B28" t="n">
-        <v>80160</v>
+        <v>91728</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468102</v>
+        <v>467620</v>
       </c>
       <c r="R28" t="n">
-        <v>7055100</v>
+        <v>7054890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,22 +3587,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130142574</v>
+        <v>130142575</v>
       </c>
       <c r="B29" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3610,34 +3610,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467620</v>
+        <v>467789</v>
       </c>
       <c r="R29" t="n">
-        <v>7054890</v>
+        <v>7054982</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3679,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Äldre Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3701,50 +3706,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130142575</v>
+        <v>130142516</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>80245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467789</v>
+        <v>468102</v>
       </c>
       <c r="R30" t="n">
-        <v>7054982</v>
+        <v>7055100</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre Ringhack</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3796,22 +3796,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130142533</v>
+        <v>130142535</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,7 +3836,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3845,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468252</v>
+        <v>467691</v>
       </c>
       <c r="R31" t="n">
-        <v>7055255</v>
+        <v>7054987</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3885,7 +3894,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>200 bålar på gammal levande gran med kådlöpa</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3913,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130142521</v>
+        <v>130130447</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3941,26 +3950,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468185</v>
+        <v>467870</v>
       </c>
       <c r="R32" t="n">
-        <v>7054913</v>
+        <v>7054963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,14 +3990,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,22 +4022,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130142535</v>
+        <v>130142533</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,16 +4062,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4070,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467691</v>
+        <v>468252</v>
       </c>
       <c r="R33" t="n">
-        <v>7054987</v>
+        <v>7055255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,7 +4111,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>200 bålar på gammal levande gran med kådlöpa</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4138,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130130447</v>
+        <v>130142521</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,17 +4167,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467870</v>
+        <v>468185</v>
       </c>
       <c r="R34" t="n">
-        <v>7054963</v>
+        <v>7054913</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,24 +4216,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4238,12 +4238,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4253,7 +4253,7 @@
         <v>130142520</v>
       </c>
       <c r="B35" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130142532</v>
+        <v>130130451</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,45 +4359,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467929</v>
+        <v>467987</v>
       </c>
       <c r="R36" t="n">
-        <v>7055015</v>
+        <v>7055415</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4427,14 +4424,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran, även liten svartspik</t>
+          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,29 +4450,43 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130142572</v>
+        <v>130142532</v>
       </c>
       <c r="B37" t="n">
-        <v>83073</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,34 +4494,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467699</v>
+        <v>467929</v>
       </c>
       <c r="R37" t="n">
-        <v>7054917</v>
+        <v>7055015</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4537,7 +4569,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>50 bålar på gammal levande gran, även liten svartspik</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,28 +4578,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130130451</v>
+        <v>130142515</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>78192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4575,42 +4608,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467987</v>
+        <v>468321</v>
       </c>
       <c r="R38" t="n">
-        <v>7055415</v>
+        <v>7055166</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4640,24 +4665,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4668,41 +4683,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130142515</v>
+        <v>130142572</v>
       </c>
       <c r="B39" t="n">
-        <v>78107</v>
+        <v>83158</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4710,21 +4710,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468321</v>
+        <v>467699</v>
       </c>
       <c r="R39" t="n">
-        <v>7055166</v>
+        <v>7054917</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4789,12 +4789,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4804,7 +4804,7 @@
         <v>130142519</v>
       </c>
       <c r="B40" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130142580</v>
+        <v>130130448</v>
       </c>
       <c r="B41" t="n">
-        <v>82939</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,34 +4910,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467784</v>
+        <v>468041</v>
       </c>
       <c r="R41" t="n">
-        <v>7054832</v>
+        <v>7054996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,14 +4967,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På två närliggande granar</t>
+          <t>Rikligare, på gran, 100-200 bålar per gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4989,22 +4999,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130142529</v>
+        <v>130142580</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>83024</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5012,36 +5022,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468113</v>
+        <v>467784</v>
       </c>
       <c r="R42" t="n">
-        <v>7055367</v>
+        <v>7054832</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5078,7 +5086,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På två närliggande granar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,29 +5095,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130142523</v>
+        <v>130142529</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5135,16 +5142,18 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467732</v>
+        <v>468113</v>
       </c>
       <c r="R43" t="n">
-        <v>7054972</v>
+        <v>7055367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5181,7 +5190,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5190,6 +5199,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5208,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130130448</v>
+        <v>130142523</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5239,14 +5249,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468041</v>
+        <v>467732</v>
       </c>
       <c r="R44" t="n">
-        <v>7054996</v>
+        <v>7054972</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5276,24 +5286,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligare, på gran, 100-200 bålar per gran</t>
+          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,22 +5308,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130142525</v>
+        <v>130130444</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,28 +5348,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467757</v>
+        <v>467755</v>
       </c>
       <c r="R45" t="n">
-        <v>7054850</v>
+        <v>7054925</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,14 +5391,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
+          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,60 +5424,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130130444</v>
+        <v>130142501</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>91692</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467755</v>
+        <v>467935</v>
       </c>
       <c r="R46" t="n">
-        <v>7054925</v>
+        <v>7055019</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,24 +5504,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
+          <t>På klen död gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5531,64 +5520,74 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130142501</v>
+        <v>130142525</v>
       </c>
       <c r="B47" t="n">
-        <v>91605</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467935</v>
+        <v>467757</v>
       </c>
       <c r="R47" t="n">
-        <v>7055019</v>
+        <v>7054850</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5624,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På klen död gran</t>
+          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5634,6 +5633,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130142504</v>
+        <v>130142534</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,16 +5681,18 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468112</v>
+        <v>467764</v>
       </c>
       <c r="R48" t="n">
-        <v>7055457</v>
+        <v>7054808</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5729,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På levande gammal grov gran i gammal granskog</t>
+          <t>På 200-årig gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5736,6 +5738,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5754,10 +5757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130142534</v>
+        <v>130142528</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5782,7 +5785,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -5791,10 +5803,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467764</v>
+        <v>467664</v>
       </c>
       <c r="R49" t="n">
-        <v>7054808</v>
+        <v>7054936</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5831,7 +5843,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På 200-årig gran i gammal granskog</t>
+          <t>400 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5859,10 +5871,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130142528</v>
+        <v>130142518</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5887,28 +5899,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467664</v>
+        <v>468111</v>
       </c>
       <c r="R50" t="n">
-        <v>7054936</v>
+        <v>7055166</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5945,7 +5946,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>400 bålar på gammal levande gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,7 +5955,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130142518</v>
+        <v>130142538</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>78192</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,34 +5984,36 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468111</v>
+        <v>468233</v>
       </c>
       <c r="R51" t="n">
-        <v>7055166</v>
+        <v>7055007</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6048,7 +6050,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6057,6 +6059,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6075,45 +6078,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130142509</v>
+        <v>130130453</v>
       </c>
       <c r="B52" t="n">
-        <v>80229</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467764</v>
+        <v>468109</v>
       </c>
       <c r="R52" t="n">
-        <v>7055038</v>
+        <v>7054902</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,14 +6146,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6165,22 +6178,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130130453</v>
+        <v>130142504</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6208,14 +6221,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468109</v>
+        <v>468112</v>
       </c>
       <c r="R53" t="n">
-        <v>7054902</v>
+        <v>7055457</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6245,24 +6258,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På levande gammal grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,62 +6280,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130142507</v>
+        <v>130142509</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>80314</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468050</v>
+        <v>467764</v>
       </c>
       <c r="R54" t="n">
-        <v>7055309</v>
+        <v>7055038</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6369,7 +6367,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6396,10 +6394,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130142538</v>
+        <v>130142507</v>
       </c>
       <c r="B55" t="n">
-        <v>78107</v>
+        <v>57826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6407,36 +6405,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468233</v>
+        <v>468050</v>
       </c>
       <c r="R55" t="n">
-        <v>7055007</v>
+        <v>7055309</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6473,7 +6474,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6482,7 +6483,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>130142578</v>
       </c>
       <c r="B56" t="n">
-        <v>78107</v>
+        <v>78192</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>130142579</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130142499</v>
+        <v>130142577</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>78192</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468254</v>
+        <v>467937</v>
       </c>
       <c r="R58" t="n">
-        <v>7054950</v>
+        <v>7054881</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6804,22 +6804,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130142577</v>
+        <v>130142499</v>
       </c>
       <c r="B59" t="n">
-        <v>78107</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6827,21 +6827,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467937</v>
+        <v>468254</v>
       </c>
       <c r="R59" t="n">
-        <v>7054881</v>
+        <v>7054950</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6906,22 +6906,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130142517</v>
+        <v>130142530</v>
       </c>
       <c r="B60" t="n">
-        <v>56922</v>
+        <v>79180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6929,38 +6929,45 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468271</v>
+        <v>468034</v>
       </c>
       <c r="R60" t="n">
-        <v>7054976</v>
+        <v>7055454</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6997,7 +7004,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>1 ex i gammal granskog</t>
+          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7006,6 +7013,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7024,10 +7032,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130142530</v>
+        <v>130142542</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7054,7 +7062,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7070,10 +7078,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468034</v>
+        <v>467980</v>
       </c>
       <c r="R61" t="n">
-        <v>7055454</v>
+        <v>7055026</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7110,7 +7118,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
+          <t>100 bålar på gammal levande gran (8 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7138,45 +7146,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130142511</v>
+        <v>130142517</v>
       </c>
       <c r="B62" t="n">
-        <v>80236</v>
+        <v>57007</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467765</v>
+        <v>468271</v>
       </c>
       <c r="R62" t="n">
-        <v>7055022</v>
+        <v>7054976</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7213,7 +7225,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>1 ex i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7240,45 +7252,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130142508</v>
+        <v>130142576</v>
       </c>
       <c r="B63" t="n">
-        <v>80229</v>
+        <v>57826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467673</v>
+        <v>467637</v>
       </c>
       <c r="R63" t="n">
-        <v>7054942</v>
+        <v>7054889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7315,7 +7332,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7330,68 +7347,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130142542</v>
+        <v>130142511</v>
       </c>
       <c r="B64" t="n">
-        <v>79095</v>
+        <v>80321</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467980</v>
+        <v>467765</v>
       </c>
       <c r="R64" t="n">
-        <v>7055026</v>
+        <v>7055022</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7428,7 +7434,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran (8 cm dbh) i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7437,7 +7443,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7456,48 +7461,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130142549</v>
+        <v>130142508</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>80314</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467791</v>
+        <v>467673</v>
       </c>
       <c r="R65" t="n">
-        <v>7054826</v>
+        <v>7054942</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7534,7 +7536,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7543,7 +7545,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7562,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130142576</v>
+        <v>130142549</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7573,39 +7574,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467637</v>
+        <v>467791</v>
       </c>
       <c r="R66" t="n">
-        <v>7054889</v>
+        <v>7054826</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7642,7 +7641,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7651,18 +7650,19 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7672,7 +7672,7 @@
         <v>130130452</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>130142544</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130142505</v>
+        <v>130142537</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,39 +1529,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468112</v>
+        <v>467722</v>
       </c>
       <c r="R10" t="n">
-        <v>7055457</v>
+        <v>7054932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
+          <t>100 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,6 +1613,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1625,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130142537</v>
+        <v>130142505</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,45 +1643,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467722</v>
+        <v>468112</v>
       </c>
       <c r="R11" t="n">
-        <v>7054932</v>
+        <v>7055457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran i gammal granskog</t>
+          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1721,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3083,45 +3083,47 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142581</v>
+        <v>130142531</v>
       </c>
       <c r="B24" t="n">
-        <v>92151</v>
+        <v>78192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467806</v>
+        <v>467929</v>
       </c>
       <c r="R24" t="n">
-        <v>7054984</v>
+        <v>7055015</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3158,7 +3160,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,65 +3169,64 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130142524</v>
+        <v>130142581</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>92151</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468176</v>
+        <v>467806</v>
       </c>
       <c r="R25" t="n">
-        <v>7055315</v>
+        <v>7054984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,7 +3263,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,26 +3272,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130142514</v>
+        <v>130142524</v>
       </c>
       <c r="B26" t="n">
         <v>79180</v>
@@ -3319,16 +3319,18 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468321</v>
+        <v>468176</v>
       </c>
       <c r="R26" t="n">
-        <v>7055166</v>
+        <v>7055315</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3374,6 +3376,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3392,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130142531</v>
+        <v>130142514</v>
       </c>
       <c r="B27" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,36 +3406,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467929</v>
+        <v>468321</v>
       </c>
       <c r="R27" t="n">
-        <v>7055015</v>
+        <v>7055166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,7 +3470,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3478,7 +3479,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -5320,56 +5320,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130142525</v>
+        <v>130142501</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467757</v>
+        <v>467935</v>
       </c>
       <c r="R45" t="n">
-        <v>7054850</v>
+        <v>7055019</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5395,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
+          <t>På klen död gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5415,7 +5404,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5434,7 +5422,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130130444</v>
+        <v>130142525</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -5462,20 +5450,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467755</v>
+        <v>467757</v>
       </c>
       <c r="R46" t="n">
-        <v>7054925</v>
+        <v>7054850</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,24 +5501,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
+          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,57 +5524,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130142501</v>
+        <v>130130444</v>
       </c>
       <c r="B47" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467935</v>
+        <v>467755</v>
       </c>
       <c r="R47" t="n">
-        <v>7055019</v>
+        <v>7054925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5618,14 +5607,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På klen död gran</t>
+          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5634,18 +5633,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130142577</v>
+        <v>130142499</v>
       </c>
       <c r="B58" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467937</v>
+        <v>468254</v>
       </c>
       <c r="R58" t="n">
-        <v>7054881</v>
+        <v>7054950</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6804,22 +6804,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130142499</v>
+        <v>130142577</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6827,21 +6827,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468254</v>
+        <v>467937</v>
       </c>
       <c r="R59" t="n">
-        <v>7054950</v>
+        <v>7054881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130142537</v>
+        <v>130142505</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,45 +1529,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467722</v>
+        <v>468112</v>
       </c>
       <c r="R10" t="n">
-        <v>7054932</v>
+        <v>7055457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1598,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran i gammal granskog</t>
+          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,7 +1607,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1632,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130142505</v>
+        <v>130142537</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,39 +1636,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468112</v>
+        <v>467722</v>
       </c>
       <c r="R11" t="n">
-        <v>7055457</v>
+        <v>7054932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1711,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
+          <t>100 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,6 +1720,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130142548</v>
+        <v>130142512</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,36 +2331,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467726</v>
+        <v>467732</v>
       </c>
       <c r="R17" t="n">
-        <v>7055026</v>
+        <v>7054900</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,7 +2395,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,7 +2404,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2425,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130130449</v>
+        <v>130142573</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,34 +2433,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468106</v>
+        <v>467742</v>
       </c>
       <c r="R18" t="n">
-        <v>7055256</v>
+        <v>7054804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,24 +2490,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>200 bålar per gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,19 +2512,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130142541</v>
+        <v>130142536</v>
       </c>
       <c r="B19" t="n">
         <v>79180</v>
@@ -2583,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468161</v>
+        <v>468265</v>
       </c>
       <c r="R19" t="n">
-        <v>7054893</v>
+        <v>7055202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2610,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>50 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,7 +2638,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130142545</v>
+        <v>130142548</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2679,16 +2666,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2697,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468004</v>
+        <v>467726</v>
       </c>
       <c r="R20" t="n">
-        <v>7055356</v>
+        <v>7055026</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,7 +2715,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>75 bålar på gammal grov gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130142573</v>
+        <v>130130449</v>
       </c>
       <c r="B21" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,34 +2754,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467742</v>
+        <v>468106</v>
       </c>
       <c r="R21" t="n">
-        <v>7054804</v>
+        <v>7055256</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,14 +2811,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>200 bålar per gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,19 +2843,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130142536</v>
+        <v>130142541</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -2913,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468265</v>
+        <v>468161</v>
       </c>
       <c r="R22" t="n">
-        <v>7055202</v>
+        <v>7054893</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2953,7 +2941,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2981,10 +2969,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130142512</v>
+        <v>130142545</v>
       </c>
       <c r="B23" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,34 +2980,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467732</v>
+        <v>468004</v>
       </c>
       <c r="R23" t="n">
-        <v>7054900</v>
+        <v>7055356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,7 +3055,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
+          <t>75 bålar på gammal grov gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,6 +3064,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3083,47 +3083,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142531</v>
+        <v>130142581</v>
       </c>
       <c r="B24" t="n">
-        <v>78192</v>
+        <v>92151</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467929</v>
+        <v>467806</v>
       </c>
       <c r="R24" t="n">
-        <v>7055015</v>
+        <v>7054984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3158,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,64 +3167,65 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130142581</v>
+        <v>130142524</v>
       </c>
       <c r="B25" t="n">
-        <v>92151</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467806</v>
+        <v>468176</v>
       </c>
       <c r="R25" t="n">
-        <v>7054984</v>
+        <v>7055315</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3262,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3272,25 +3271,26 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130142524</v>
+        <v>130142514</v>
       </c>
       <c r="B26" t="n">
         <v>79180</v>
@@ -3319,18 +3319,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468176</v>
+        <v>468321</v>
       </c>
       <c r="R26" t="n">
-        <v>7055315</v>
+        <v>7055166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3365,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3376,7 +3374,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3395,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130142514</v>
+        <v>130142531</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3406,34 +3403,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468321</v>
+        <v>467929</v>
       </c>
       <c r="R27" t="n">
-        <v>7055166</v>
+        <v>7055015</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3469,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,6 +3478,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4348,10 +4348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130142515</v>
+        <v>130142532</v>
       </c>
       <c r="B36" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,34 +4359,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>468321</v>
+        <v>467929</v>
       </c>
       <c r="R36" t="n">
-        <v>7055166</v>
+        <v>7055015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4423,7 +4434,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal levande gran, även liten svartspik</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4432,6 +4443,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4552,10 +4564,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130142532</v>
+        <v>130130451</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,45 +4575,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467929</v>
+        <v>467987</v>
       </c>
       <c r="R38" t="n">
-        <v>7055015</v>
+        <v>7055415</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4631,14 +4640,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran, även liten svartspik</t>
+          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4647,29 +4666,43 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130130451</v>
+        <v>130142515</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>78192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4677,42 +4710,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467987</v>
+        <v>468321</v>
       </c>
       <c r="R39" t="n">
-        <v>7055415</v>
+        <v>7055166</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4742,24 +4767,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,31 +4785,16 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5320,45 +5320,56 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130142501</v>
+        <v>130142525</v>
       </c>
       <c r="B45" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467935</v>
+        <v>467757</v>
       </c>
       <c r="R45" t="n">
-        <v>7055019</v>
+        <v>7054850</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5395,7 +5406,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På klen död gran</t>
+          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5404,6 +5415,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5422,7 +5434,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130142525</v>
+        <v>130130444</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -5450,28 +5462,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467757</v>
+        <v>467755</v>
       </c>
       <c r="R46" t="n">
-        <v>7054850</v>
+        <v>7054925</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5501,14 +5505,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
+          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5524,60 +5538,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130130444</v>
+        <v>130142501</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467755</v>
+        <v>467935</v>
       </c>
       <c r="R47" t="n">
-        <v>7054925</v>
+        <v>7055019</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5607,24 +5618,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
+          <t>På klen död gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5633,29 +5634,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130142538</v>
+        <v>130142528</v>
       </c>
       <c r="B48" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5663,24 +5663,33 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -5689,10 +5698,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468233</v>
+        <v>467664</v>
       </c>
       <c r="R48" t="n">
-        <v>7055007</v>
+        <v>7054936</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5729,7 +5738,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>400 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5757,7 +5766,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130142534</v>
+        <v>130142518</v>
       </c>
       <c r="B49" t="n">
         <v>79180</v>
@@ -5786,18 +5795,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467764</v>
+        <v>468111</v>
       </c>
       <c r="R49" t="n">
-        <v>7054808</v>
+        <v>7055166</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5841,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På 200-årig gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5843,7 +5850,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5862,7 +5868,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130130453</v>
+        <v>130142534</v>
       </c>
       <c r="B50" t="n">
         <v>79180</v>
@@ -5891,16 +5897,18 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468109</v>
+        <v>467764</v>
       </c>
       <c r="R50" t="n">
-        <v>7054902</v>
+        <v>7054808</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5930,24 +5938,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På 200-årig gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,25 +5954,26 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130142504</v>
+        <v>130130453</v>
       </c>
       <c r="B51" t="n">
         <v>79180</v>
@@ -6005,14 +6004,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468112</v>
+        <v>468109</v>
       </c>
       <c r="R51" t="n">
-        <v>7055457</v>
+        <v>7054902</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6042,14 +6041,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På levande gammal grov gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6064,44 +6073,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130142509</v>
+        <v>130142504</v>
       </c>
       <c r="B52" t="n">
-        <v>80314</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6111,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467764</v>
+        <v>468112</v>
       </c>
       <c r="R52" t="n">
-        <v>7055038</v>
+        <v>7055457</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6151,7 +6160,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På levande gammal grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6178,50 +6187,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130142507</v>
+        <v>130142509</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468050</v>
+        <v>467764</v>
       </c>
       <c r="R53" t="n">
-        <v>7055309</v>
+        <v>7055038</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6258,7 +6262,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6285,10 +6289,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130142528</v>
+        <v>130142507</v>
       </c>
       <c r="B54" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6296,45 +6300,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467664</v>
+        <v>468050</v>
       </c>
       <c r="R54" t="n">
-        <v>7054936</v>
+        <v>7055309</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6371,7 +6369,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>400 bålar på gammal levande gran i gammal granskog</t>
+          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6380,7 +6378,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6399,10 +6396,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130142518</v>
+        <v>130142538</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6410,34 +6407,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468111</v>
+        <v>468233</v>
       </c>
       <c r="R55" t="n">
-        <v>7055166</v>
+        <v>7055007</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6474,7 +6473,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6483,6 +6482,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130142579</v>
+        <v>130142578</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6512,43 +6512,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467640</v>
+        <v>467794</v>
       </c>
       <c r="R56" t="n">
-        <v>7054887</v>
+        <v>7054821</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6585,7 +6576,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1000 ex på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6612,10 +6603,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130142578</v>
+        <v>130142579</v>
       </c>
       <c r="B57" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6623,34 +6614,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467794</v>
+        <v>467640</v>
       </c>
       <c r="R57" t="n">
-        <v>7054821</v>
+        <v>7054887</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1000 ex på gammal gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6714,10 +6714,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130142499</v>
+        <v>130142577</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468254</v>
+        <v>467937</v>
       </c>
       <c r="R58" t="n">
-        <v>7054950</v>
+        <v>7054881</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6804,22 +6804,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130142577</v>
+        <v>130142499</v>
       </c>
       <c r="B59" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6827,21 +6827,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467937</v>
+        <v>468254</v>
       </c>
       <c r="R59" t="n">
-        <v>7054881</v>
+        <v>7054950</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130142510</v>
+        <v>130142500</v>
       </c>
       <c r="B6" t="n">
-        <v>80286</v>
+        <v>91692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467764</v>
+        <v>468254</v>
       </c>
       <c r="R6" t="n">
-        <v>7055038</v>
+        <v>7054950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,45 +1206,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142500</v>
+        <v>130142526</v>
       </c>
       <c r="B7" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468254</v>
+        <v>468039</v>
       </c>
       <c r="R7" t="n">
-        <v>7054950</v>
+        <v>7055284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1283,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,6 +1292,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1308,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142526</v>
+        <v>130142540</v>
       </c>
       <c r="B8" t="n">
         <v>79180</v>
@@ -1345,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468039</v>
+        <v>468101</v>
       </c>
       <c r="R8" t="n">
-        <v>7055284</v>
+        <v>7054854</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,7 +1388,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130142540</v>
+        <v>130142510</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>80286</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,36 +1427,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468101</v>
+        <v>467764</v>
       </c>
       <c r="R9" t="n">
-        <v>7054854</v>
+        <v>7055038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1491,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,7 +1500,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130142505</v>
+        <v>130142537</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,39 +1529,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468112</v>
+        <v>467722</v>
       </c>
       <c r="R10" t="n">
-        <v>7055457</v>
+        <v>7054932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
+          <t>100 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,6 +1613,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1625,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130142537</v>
+        <v>130142505</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,45 +1643,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467722</v>
+        <v>468112</v>
       </c>
       <c r="R11" t="n">
-        <v>7054932</v>
+        <v>7055457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran i gammal granskog</t>
+          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1721,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130142533</v>
+        <v>130130447</v>
       </c>
       <c r="B31" t="n">
         <v>79180</v>
@@ -3837,18 +3837,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468252</v>
+        <v>467870</v>
       </c>
       <c r="R31" t="n">
-        <v>7055255</v>
+        <v>7054963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,14 +3876,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3894,26 +3902,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130142521</v>
+        <v>130142535</v>
       </c>
       <c r="B32" t="n">
         <v>79180</v>
@@ -3943,7 +3950,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3951,16 +3958,18 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468185</v>
+        <v>467691</v>
       </c>
       <c r="R32" t="n">
-        <v>7054913</v>
+        <v>7054987</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,7 +4006,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>200 bålar på gammal levande gran med kådlöpa</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,6 +4015,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4024,7 +4034,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130142535</v>
+        <v>130142533</v>
       </c>
       <c r="B33" t="n">
         <v>79180</v>
@@ -4052,16 +4062,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4070,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467691</v>
+        <v>468252</v>
       </c>
       <c r="R33" t="n">
-        <v>7054987</v>
+        <v>7055255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,7 +4111,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>200 bålar på gammal levande gran med kådlöpa</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4138,7 +4139,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130130447</v>
+        <v>130142521</v>
       </c>
       <c r="B34" t="n">
         <v>79180</v>
@@ -4166,17 +4167,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467870</v>
+        <v>468185</v>
       </c>
       <c r="R34" t="n">
-        <v>7054963</v>
+        <v>7054913</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,24 +4216,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4238,12 +4238,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130142532</v>
+        <v>130142515</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,45 +4359,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467929</v>
+        <v>468321</v>
       </c>
       <c r="R36" t="n">
-        <v>7055015</v>
+        <v>7055166</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4434,7 +4423,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran, även liten svartspik</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,7 +4432,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4564,10 +4552,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130130451</v>
+        <v>130142532</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4575,42 +4563,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467987</v>
+        <v>467929</v>
       </c>
       <c r="R38" t="n">
-        <v>7055415</v>
+        <v>7055015</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4640,24 +4631,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
+          <t>50 bålar på gammal levande gran, även liten svartspik</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4666,43 +4647,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130142515</v>
+        <v>130130451</v>
       </c>
       <c r="B39" t="n">
-        <v>78192</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4710,34 +4677,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468321</v>
+        <v>467987</v>
       </c>
       <c r="R39" t="n">
-        <v>7055166</v>
+        <v>7055415</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4767,14 +4742,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4785,16 +4770,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5320,56 +5320,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130142525</v>
+        <v>130142501</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467757</v>
+        <v>467935</v>
       </c>
       <c r="R45" t="n">
-        <v>7054850</v>
+        <v>7055019</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5395,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
+          <t>På klen död gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5415,7 +5404,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5434,7 +5422,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130130444</v>
+        <v>130142525</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -5462,20 +5450,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467755</v>
+        <v>467757</v>
       </c>
       <c r="R46" t="n">
-        <v>7054925</v>
+        <v>7054850</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,24 +5501,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
+          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,57 +5524,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130142501</v>
+        <v>130130444</v>
       </c>
       <c r="B47" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467935</v>
+        <v>467755</v>
       </c>
       <c r="R47" t="n">
-        <v>7055019</v>
+        <v>7054925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5618,14 +5607,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På klen död gran</t>
+          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5634,18 +5633,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130142544</v>
+        <v>130130452</v>
       </c>
       <c r="B67" t="n">
         <v>79180</v>
@@ -7698,18 +7698,16 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468267</v>
+        <v>468256</v>
       </c>
       <c r="R67" t="n">
-        <v>7055127</v>
+        <v>7055180</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7739,14 +7737,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ca 50-100 bålar per gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7755,26 +7763,25 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130130452</v>
+        <v>130142544</v>
       </c>
       <c r="B68" t="n">
         <v>79180</v>
@@ -7803,16 +7810,18 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468256</v>
+        <v>468267</v>
       </c>
       <c r="R68" t="n">
-        <v>7055180</v>
+        <v>7055127</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,24 +7851,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ca 50-100 bålar per gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7868,18 +7867,19 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142506</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130142502</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130142522</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130142527</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>130142500</v>
       </c>
       <c r="B6" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142526</v>
+        <v>130142540</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468039</v>
+        <v>468101</v>
       </c>
       <c r="R7" t="n">
-        <v>7055284</v>
+        <v>7054854</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142540</v>
+        <v>130142526</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468101</v>
+        <v>468039</v>
       </c>
       <c r="R8" t="n">
-        <v>7054854</v>
+        <v>7055284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
         <v>130142510</v>
       </c>
       <c r="B9" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>130142537</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1874,48 +1874,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130130446</v>
+        <v>130130445</v>
       </c>
       <c r="B13" t="n">
-        <v>92446</v>
+        <v>91751</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467827</v>
+        <v>467790</v>
       </c>
       <c r="R13" t="n">
-        <v>7054966</v>
+        <v>7054972</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1940,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,12 +1950,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Torraka av gran</t>
+          <t>Högstubbe, gran, med födosök från hackspett</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,24 +1964,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2005,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130130445</v>
+        <v>130142539</v>
       </c>
       <c r="B14" t="n">
-        <v>91748</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,30 +1993,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467790</v>
+        <v>468233</v>
       </c>
       <c r="R14" t="n">
-        <v>7054972</v>
+        <v>7055007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,24 +2052,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Högstubbe, gran, med födosök från hackspett</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,28 +2068,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130142539</v>
+        <v>130142513</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>83161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,36 +2098,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468233</v>
+        <v>468321</v>
       </c>
       <c r="R15" t="n">
-        <v>7055007</v>
+        <v>7055166</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,7 +2162,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,7 +2171,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2218,45 +2189,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130142513</v>
+        <v>130130446</v>
       </c>
       <c r="B16" t="n">
-        <v>83158</v>
+        <v>92449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468321</v>
+        <v>467827</v>
       </c>
       <c r="R16" t="n">
-        <v>7055166</v>
+        <v>7054966</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,14 +2260,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Torraka av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,28 +2286,44 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130142512</v>
+        <v>130142573</v>
       </c>
       <c r="B17" t="n">
-        <v>78192</v>
+        <v>91731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467732</v>
+        <v>467742</v>
       </c>
       <c r="R17" t="n">
-        <v>7054900</v>
+        <v>7054804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,22 +2410,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130142573</v>
+        <v>130142545</v>
       </c>
       <c r="B18" t="n">
-        <v>91728</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,34 +2433,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467742</v>
+        <v>468004</v>
       </c>
       <c r="R18" t="n">
-        <v>7054804</v>
+        <v>7055356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,7 +2508,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>75 bålar på gammal grov gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,28 +2517,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130142536</v>
+        <v>130142541</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468265</v>
+        <v>468161</v>
       </c>
       <c r="R19" t="n">
-        <v>7055202</v>
+        <v>7054893</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2610,7 +2622,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,7 +2653,7 @@
         <v>130142548</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,10 +2755,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130130449</v>
+        <v>130142536</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,17 +2783,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468106</v>
+        <v>468265</v>
       </c>
       <c r="R21" t="n">
-        <v>7055256</v>
+        <v>7055202</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,24 +2834,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>200 bålar per gran</t>
+          <t>50 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,28 +2850,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130142541</v>
+        <v>130130449</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2883,28 +2897,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468161</v>
+        <v>468106</v>
       </c>
       <c r="R22" t="n">
-        <v>7054893</v>
+        <v>7055256</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,14 +2937,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>200 bålar per gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,29 +2963,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130142545</v>
+        <v>130142512</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>78195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2980,45 +2992,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468004</v>
+        <v>467732</v>
       </c>
       <c r="R23" t="n">
-        <v>7055356</v>
+        <v>7054900</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3055,7 +3056,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>75 bålar på gammal grov gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,7 +3065,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3083,45 +3083,47 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142581</v>
+        <v>130142524</v>
       </c>
       <c r="B24" t="n">
-        <v>92151</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467806</v>
+        <v>468176</v>
       </c>
       <c r="R24" t="n">
-        <v>7054984</v>
+        <v>7055315</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3158,7 +3160,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,28 +3169,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130142524</v>
+        <v>130142514</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,18 +3217,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468176</v>
+        <v>468321</v>
       </c>
       <c r="R25" t="n">
-        <v>7055315</v>
+        <v>7055166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,7 +3263,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,7 +3272,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130142514</v>
+        <v>130142581</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>92154</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468321</v>
+        <v>467806</v>
       </c>
       <c r="R26" t="n">
-        <v>7055166</v>
+        <v>7054984</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3380,12 +3380,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
         <v>130142531</v>
       </c>
       <c r="B27" t="n">
-        <v>78192</v>
+        <v>78195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,45 +3497,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130142516</v>
+        <v>130142575</v>
       </c>
       <c r="B28" t="n">
-        <v>80245</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468102</v>
+        <v>467789</v>
       </c>
       <c r="R28" t="n">
-        <v>7055100</v>
+        <v>7054982</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3572,7 +3577,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Äldre Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,12 +3592,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3602,7 +3607,7 @@
         <v>130142574</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3701,50 +3706,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130142575</v>
+        <v>130142516</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>80248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467789</v>
+        <v>468102</v>
       </c>
       <c r="R30" t="n">
-        <v>7054982</v>
+        <v>7055100</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre Ringhack</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3796,22 +3796,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130130447</v>
+        <v>130142533</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,16 +3837,18 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467870</v>
+        <v>468252</v>
       </c>
       <c r="R31" t="n">
-        <v>7054963</v>
+        <v>7055255</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3876,24 +3878,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3902,28 +3894,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130142535</v>
+        <v>130142521</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3943,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3958,18 +3951,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467691</v>
+        <v>468185</v>
       </c>
       <c r="R32" t="n">
-        <v>7054987</v>
+        <v>7054913</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4006,7 +3997,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>200 bålar på gammal levande gran med kådlöpa</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4015,7 +4006,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4034,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130142533</v>
+        <v>130142535</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4062,7 +4052,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4071,10 +4070,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468252</v>
+        <v>467691</v>
       </c>
       <c r="R33" t="n">
-        <v>7055255</v>
+        <v>7054987</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4111,7 +4110,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>200 bålar på gammal levande gran med kådlöpa</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,10 +4138,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130142521</v>
+        <v>130130447</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4167,26 +4166,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468185</v>
+        <v>467870</v>
       </c>
       <c r="R34" t="n">
-        <v>7054913</v>
+        <v>7054963</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4216,14 +4206,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4238,12 +4238,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4253,7 +4253,7 @@
         <v>130142520</v>
       </c>
       <c r="B35" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130142515</v>
+        <v>130142532</v>
       </c>
       <c r="B36" t="n">
-        <v>78192</v>
+        <v>79183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,34 +4359,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>468321</v>
+        <v>467929</v>
       </c>
       <c r="R36" t="n">
-        <v>7055166</v>
+        <v>7055015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4423,7 +4434,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal levande gran, även liten svartspik</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4432,6 +4443,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4453,7 +4465,7 @@
         <v>130142572</v>
       </c>
       <c r="B37" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4552,10 +4564,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130142532</v>
+        <v>130130451</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,45 +4575,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467929</v>
+        <v>467987</v>
       </c>
       <c r="R38" t="n">
-        <v>7055015</v>
+        <v>7055415</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4631,14 +4640,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran, även liten svartspik</t>
+          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4647,29 +4666,43 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130130451</v>
+        <v>130142515</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>78195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4677,42 +4710,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467987</v>
+        <v>468321</v>
       </c>
       <c r="R39" t="n">
-        <v>7055415</v>
+        <v>7055166</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4742,24 +4767,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,31 +4785,16 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4804,7 +4804,7 @@
         <v>130142519</v>
       </c>
       <c r="B40" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130142580</v>
+        <v>130142529</v>
       </c>
       <c r="B41" t="n">
-        <v>83024</v>
+        <v>79183</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,34 +4910,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467784</v>
+        <v>468113</v>
       </c>
       <c r="R41" t="n">
-        <v>7054832</v>
+        <v>7055367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4974,7 +4976,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På två närliggande granar</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4983,28 +4985,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130142529</v>
+        <v>130142523</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,18 +5033,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468113</v>
+        <v>467732</v>
       </c>
       <c r="R42" t="n">
-        <v>7055367</v>
+        <v>7054972</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5078,7 +5079,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,7 +5088,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130142523</v>
+        <v>130130448</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,14 +5137,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467732</v>
+        <v>468041</v>
       </c>
       <c r="R43" t="n">
-        <v>7054972</v>
+        <v>7054996</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,14 +5174,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
+          <t>Rikligare, på gran, 100-200 bålar per gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5196,22 +5206,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130130448</v>
+        <v>130142580</v>
       </c>
       <c r="B44" t="n">
-        <v>79180</v>
+        <v>83027</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5219,34 +5229,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468041</v>
+        <v>467784</v>
       </c>
       <c r="R44" t="n">
-        <v>7054996</v>
+        <v>7054832</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5276,24 +5286,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligare, på gran, 100-200 bålar per gran</t>
+          <t>På två närliggande granar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,57 +5308,68 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130142501</v>
+        <v>130142525</v>
       </c>
       <c r="B45" t="n">
-        <v>91692</v>
+        <v>79183</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467935</v>
+        <v>467757</v>
       </c>
       <c r="R45" t="n">
-        <v>7055019</v>
+        <v>7054850</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5395,7 +5406,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På klen död gran</t>
+          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5404,6 +5415,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5422,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130142525</v>
+        <v>130130444</v>
       </c>
       <c r="B46" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,28 +5462,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467757</v>
+        <v>467755</v>
       </c>
       <c r="R46" t="n">
-        <v>7054850</v>
+        <v>7054925</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5501,14 +5505,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
+          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5524,60 +5538,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130130444</v>
+        <v>130142501</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>91695</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467755</v>
+        <v>467935</v>
       </c>
       <c r="R47" t="n">
-        <v>7054925</v>
+        <v>7055019</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5607,24 +5618,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
+          <t>På klen död gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5633,29 +5634,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130142528</v>
+        <v>130142504</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5680,28 +5680,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467664</v>
+        <v>468112</v>
       </c>
       <c r="R48" t="n">
-        <v>7054936</v>
+        <v>7055457</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5738,7 +5727,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>400 bålar på gammal levande gran i gammal granskog</t>
+          <t>På levande gammal grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5747,7 +5736,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5766,10 +5754,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130142518</v>
+        <v>130142534</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,16 +5783,18 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468111</v>
+        <v>467764</v>
       </c>
       <c r="R49" t="n">
-        <v>7055166</v>
+        <v>7054808</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5831,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På 200-årig gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5850,6 +5840,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5868,10 +5859,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130142534</v>
+        <v>130142528</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5896,7 +5887,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -5905,10 +5905,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467764</v>
+        <v>467664</v>
       </c>
       <c r="R50" t="n">
-        <v>7054808</v>
+        <v>7054936</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På 200-årig gran i gammal granskog</t>
+          <t>400 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5973,10 +5973,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130130453</v>
+        <v>130142518</v>
       </c>
       <c r="B51" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6004,14 +6004,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468109</v>
+        <v>468111</v>
       </c>
       <c r="R51" t="n">
-        <v>7054902</v>
+        <v>7055166</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6041,24 +6041,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6073,22 +6063,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130142504</v>
+        <v>130130453</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6116,14 +6106,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468112</v>
+        <v>468109</v>
       </c>
       <c r="R52" t="n">
-        <v>7055457</v>
+        <v>7054902</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6153,14 +6143,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På levande gammal grov gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,57 +6175,62 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130142509</v>
+        <v>130142507</v>
       </c>
       <c r="B53" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467764</v>
+        <v>468050</v>
       </c>
       <c r="R53" t="n">
-        <v>7055038</v>
+        <v>7055309</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6262,7 +6267,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6289,50 +6294,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130142507</v>
+        <v>130142509</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>80317</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468050</v>
+        <v>467764</v>
       </c>
       <c r="R54" t="n">
-        <v>7055309</v>
+        <v>7055038</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6399,7 +6399,7 @@
         <v>130142538</v>
       </c>
       <c r="B55" t="n">
-        <v>78192</v>
+        <v>78195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130142578</v>
+        <v>130142579</v>
       </c>
       <c r="B56" t="n">
-        <v>78192</v>
+        <v>79183</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6512,34 +6512,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467794</v>
+        <v>467640</v>
       </c>
       <c r="R56" t="n">
-        <v>7054821</v>
+        <v>7054887</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6576,7 +6585,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1000 ex på gammal gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6603,10 +6612,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130142579</v>
+        <v>130142578</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>78195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6614,43 +6623,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467640</v>
+        <v>467794</v>
       </c>
       <c r="R57" t="n">
-        <v>7054887</v>
+        <v>7054821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>1000 ex på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6714,10 +6714,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130142577</v>
+        <v>130142499</v>
       </c>
       <c r="B58" t="n">
-        <v>78192</v>
+        <v>79183</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467937</v>
+        <v>468254</v>
       </c>
       <c r="R58" t="n">
-        <v>7054881</v>
+        <v>7054950</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6804,22 +6804,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130142499</v>
+        <v>130142577</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>78195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6827,21 +6827,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468254</v>
+        <v>467937</v>
       </c>
       <c r="R59" t="n">
-        <v>7054950</v>
+        <v>7054881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6906,61 +6906,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130142517</v>
+        <v>130142511</v>
       </c>
       <c r="B60" t="n">
-        <v>57007</v>
+        <v>80324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468271</v>
+        <v>467765</v>
       </c>
       <c r="R60" t="n">
-        <v>7054976</v>
+        <v>7055022</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6997,7 +6993,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>1 ex i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7024,48 +7020,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130142549</v>
+        <v>130142508</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>80317</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467791</v>
+        <v>467673</v>
       </c>
       <c r="R61" t="n">
-        <v>7054826</v>
+        <v>7054942</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7102,7 +7095,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7111,7 +7104,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7130,10 +7122,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130142530</v>
+        <v>130142517</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>57007</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7141,45 +7133,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468034</v>
+        <v>468271</v>
       </c>
       <c r="R62" t="n">
-        <v>7055454</v>
+        <v>7054976</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7216,7 +7201,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
+          <t>1 ex i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7225,7 +7210,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7244,10 +7228,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130142542</v>
+        <v>130142530</v>
       </c>
       <c r="B63" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7274,7 +7258,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7290,10 +7274,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467980</v>
+        <v>468034</v>
       </c>
       <c r="R63" t="n">
-        <v>7055026</v>
+        <v>7055454</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7330,7 +7314,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran (8 cm dbh) i gammal granskog</t>
+          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7358,45 +7342,56 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130142511</v>
+        <v>130142542</v>
       </c>
       <c r="B64" t="n">
-        <v>80321</v>
+        <v>79183</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467765</v>
+        <v>467980</v>
       </c>
       <c r="R64" t="n">
-        <v>7055022</v>
+        <v>7055026</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7433,7 +7428,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>100 bålar på gammal levande gran (8 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7442,6 +7437,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7460,45 +7456,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130142508</v>
+        <v>130142549</v>
       </c>
       <c r="B65" t="n">
-        <v>80314</v>
+        <v>79183</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467673</v>
+        <v>467791</v>
       </c>
       <c r="R65" t="n">
-        <v>7054942</v>
+        <v>7054826</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7535,7 +7534,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7544,6 +7543,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>130130452</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>130142544</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130142506</v>
+        <v>130142527</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,17 +703,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468050</v>
+        <v>468067</v>
       </c>
       <c r="R2" t="n">
-        <v>7055309</v>
+        <v>7055001</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>100 bålar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,7 +792,7 @@
         <v>130142502</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130142522</v>
+        <v>130142506</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,26 +919,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468134</v>
+        <v>468050</v>
       </c>
       <c r="R4" t="n">
-        <v>7054850</v>
+        <v>7055309</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +966,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130142527</v>
+        <v>130142522</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,18 +1031,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468067</v>
+        <v>468134</v>
       </c>
       <c r="R5" t="n">
-        <v>7055001</v>
+        <v>7054850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1077,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran</t>
+          <t>100 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,45 +1104,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130142500</v>
+        <v>130142540</v>
       </c>
       <c r="B6" t="n">
-        <v>91695</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468254</v>
+        <v>468101</v>
       </c>
       <c r="R6" t="n">
-        <v>7054950</v>
+        <v>7054854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1181,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,6 +1190,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142540</v>
+        <v>130142526</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468101</v>
+        <v>468039</v>
       </c>
       <c r="R7" t="n">
-        <v>7054854</v>
+        <v>7055284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1286,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142526</v>
+        <v>130142510</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>80315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,36 +1325,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468039</v>
+        <v>467764</v>
       </c>
       <c r="R8" t="n">
-        <v>7055284</v>
+        <v>7055038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1389,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,7 +1398,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130142510</v>
+        <v>130142500</v>
       </c>
       <c r="B9" t="n">
-        <v>80289</v>
+        <v>91721</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467764</v>
+        <v>468254</v>
       </c>
       <c r="R9" t="n">
-        <v>7055038</v>
+        <v>7054950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
         <v>130142537</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>130142505</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>130130450</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130130445</v>
+        <v>130142539</v>
       </c>
       <c r="B13" t="n">
-        <v>91751</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1885,30 +1885,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467790</v>
+        <v>468233</v>
       </c>
       <c r="R13" t="n">
-        <v>7054972</v>
+        <v>7055007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,24 +1944,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Högstubbe, gran, med födosök från hackspett</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,28 +1960,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130142539</v>
+        <v>130130445</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>91777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,36 +1990,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468233</v>
+        <v>467790</v>
       </c>
       <c r="R14" t="n">
-        <v>7055007</v>
+        <v>7054972</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,14 +2043,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Högstubbe, gran, med födosök från hackspett</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,19 +2069,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2090,7 +2090,7 @@
         <v>130142513</v>
       </c>
       <c r="B15" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>130130446</v>
       </c>
       <c r="B16" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130142573</v>
+        <v>130142512</v>
       </c>
       <c r="B17" t="n">
-        <v>91731</v>
+        <v>78221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467742</v>
+        <v>467732</v>
       </c>
       <c r="R17" t="n">
-        <v>7054804</v>
+        <v>7054900</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,22 +2410,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130142545</v>
+        <v>130142573</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,45 +2433,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468004</v>
+        <v>467742</v>
       </c>
       <c r="R18" t="n">
-        <v>7055356</v>
+        <v>7054804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2497,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>75 bålar på gammal grov gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,29 +2506,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130142541</v>
+        <v>130142548</v>
       </c>
       <c r="B19" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,16 +2552,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2582,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468161</v>
+        <v>467726</v>
       </c>
       <c r="R19" t="n">
-        <v>7054893</v>
+        <v>7055026</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2622,7 +2601,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130142548</v>
+        <v>130130449</v>
       </c>
       <c r="B20" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2679,18 +2658,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467726</v>
+        <v>468106</v>
       </c>
       <c r="R20" t="n">
-        <v>7055026</v>
+        <v>7055256</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,14 +2697,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>200 bålar per gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,19 +2723,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2758,7 +2744,7 @@
         <v>130142536</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130130449</v>
+        <v>130142541</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,17 +2883,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468106</v>
+        <v>468161</v>
       </c>
       <c r="R22" t="n">
-        <v>7055256</v>
+        <v>7054893</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,24 +2934,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>200 bålar per gran</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,28 +2950,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130142512</v>
+        <v>130142545</v>
       </c>
       <c r="B23" t="n">
-        <v>78195</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,34 +2980,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467732</v>
+        <v>468004</v>
       </c>
       <c r="R23" t="n">
-        <v>7054900</v>
+        <v>7055356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,7 +3055,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
+          <t>75 bålar på gammal grov gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,6 +3064,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3083,47 +3083,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142524</v>
+        <v>130142581</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>92180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468176</v>
+        <v>467806</v>
       </c>
       <c r="R24" t="n">
-        <v>7055315</v>
+        <v>7054984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3158,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,19 +3167,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3191,7 +3188,7 @@
         <v>130142514</v>
       </c>
       <c r="B25" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,45 +3287,47 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130142581</v>
+        <v>130142524</v>
       </c>
       <c r="B26" t="n">
-        <v>92154</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467806</v>
+        <v>468176</v>
       </c>
       <c r="R26" t="n">
-        <v>7054984</v>
+        <v>7055315</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,7 +3364,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3374,18 +3373,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
         <v>130142531</v>
       </c>
       <c r="B27" t="n">
-        <v>78195</v>
+        <v>78221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>130142575</v>
       </c>
       <c r="B28" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>130142574</v>
       </c>
       <c r="B29" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>130142516</v>
       </c>
       <c r="B30" t="n">
-        <v>80248</v>
+        <v>80274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130142533</v>
+        <v>130130447</v>
       </c>
       <c r="B31" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,18 +3837,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468252</v>
+        <v>467870</v>
       </c>
       <c r="R31" t="n">
-        <v>7055255</v>
+        <v>7054963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,14 +3876,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3894,29 +3902,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130142521</v>
+        <v>130142533</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3941,26 +3948,19 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468185</v>
+        <v>468252</v>
       </c>
       <c r="R32" t="n">
-        <v>7054913</v>
+        <v>7055255</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,6 +4006,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4027,7 +4028,7 @@
         <v>130142535</v>
       </c>
       <c r="B33" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4138,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130130447</v>
+        <v>130142521</v>
       </c>
       <c r="B34" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,17 +4167,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467870</v>
+        <v>468185</v>
       </c>
       <c r="R34" t="n">
-        <v>7054963</v>
+        <v>7054913</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,24 +4216,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4238,12 +4238,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4253,7 +4253,7 @@
         <v>130142520</v>
       </c>
       <c r="B35" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130142532</v>
+        <v>130142515</v>
       </c>
       <c r="B36" t="n">
-        <v>79183</v>
+        <v>78221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,45 +4359,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467929</v>
+        <v>468321</v>
       </c>
       <c r="R36" t="n">
-        <v>7055015</v>
+        <v>7055166</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4434,7 +4423,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran, även liten svartspik</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,7 +4432,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4465,7 +4453,7 @@
         <v>130142572</v>
       </c>
       <c r="B37" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4567,7 +4555,7 @@
         <v>130130451</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4699,10 +4687,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130142515</v>
+        <v>130142532</v>
       </c>
       <c r="B39" t="n">
-        <v>78195</v>
+        <v>79209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4710,34 +4698,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468321</v>
+        <v>467929</v>
       </c>
       <c r="R39" t="n">
-        <v>7055166</v>
+        <v>7055015</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4774,7 +4773,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal levande gran, även liten svartspik</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4783,6 +4782,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>130142519</v>
       </c>
       <c r="B40" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130142529</v>
+        <v>130142580</v>
       </c>
       <c r="B41" t="n">
-        <v>79183</v>
+        <v>83053</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,36 +4910,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468113</v>
+        <v>467784</v>
       </c>
       <c r="R41" t="n">
-        <v>7055367</v>
+        <v>7054832</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4976,7 +4974,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På två närliggande granar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4985,29 +4983,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130142523</v>
+        <v>130130448</v>
       </c>
       <c r="B42" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5035,14 +5032,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467732</v>
+        <v>468041</v>
       </c>
       <c r="R42" t="n">
-        <v>7054972</v>
+        <v>7054996</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5072,14 +5069,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
+          <t>Rikligare, på gran, 100-200 bålar per gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5094,22 +5101,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130130448</v>
+        <v>130142523</v>
       </c>
       <c r="B43" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,14 +5144,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468041</v>
+        <v>467732</v>
       </c>
       <c r="R43" t="n">
-        <v>7054996</v>
+        <v>7054972</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,24 +5181,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligare, på gran, 100-200 bålar per gran</t>
+          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5206,22 +5203,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130142580</v>
+        <v>130142529</v>
       </c>
       <c r="B44" t="n">
-        <v>83027</v>
+        <v>79209</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,34 +5226,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467784</v>
+        <v>468113</v>
       </c>
       <c r="R44" t="n">
-        <v>7054832</v>
+        <v>7055367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5292,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På två närliggande granar</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,28 +5301,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130142525</v>
+        <v>130130444</v>
       </c>
       <c r="B45" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,28 +5348,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467757</v>
+        <v>467755</v>
       </c>
       <c r="R45" t="n">
-        <v>7054850</v>
+        <v>7054925</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,14 +5391,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
+          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,60 +5424,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130130444</v>
+        <v>130142501</v>
       </c>
       <c r="B46" t="n">
-        <v>79183</v>
+        <v>91721</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467755</v>
+        <v>467935</v>
       </c>
       <c r="R46" t="n">
-        <v>7054925</v>
+        <v>7055019</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,24 +5504,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
+          <t>På klen död gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5531,64 +5520,74 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130142501</v>
+        <v>130142525</v>
       </c>
       <c r="B47" t="n">
-        <v>91695</v>
+        <v>79209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467935</v>
+        <v>467757</v>
       </c>
       <c r="R47" t="n">
-        <v>7055019</v>
+        <v>7054850</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5624,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På klen död gran</t>
+          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5634,6 +5633,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130142504</v>
+        <v>130142538</v>
       </c>
       <c r="B48" t="n">
-        <v>79183</v>
+        <v>78221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5663,34 +5663,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468112</v>
+        <v>468233</v>
       </c>
       <c r="R48" t="n">
-        <v>7055457</v>
+        <v>7055007</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5729,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På levande gammal grov gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5736,6 +5738,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5757,7 +5760,7 @@
         <v>130142534</v>
       </c>
       <c r="B49" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5859,10 +5862,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130142528</v>
+        <v>130130453</v>
       </c>
       <c r="B50" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5887,28 +5890,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467664</v>
+        <v>468109</v>
       </c>
       <c r="R50" t="n">
-        <v>7054936</v>
+        <v>7054902</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5938,14 +5930,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>400 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,19 +5956,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5976,7 +5977,7 @@
         <v>130142518</v>
       </c>
       <c r="B51" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6075,10 +6076,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130130453</v>
+        <v>130142504</v>
       </c>
       <c r="B52" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6106,14 +6107,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468109</v>
+        <v>468112</v>
       </c>
       <c r="R52" t="n">
-        <v>7054902</v>
+        <v>7055457</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,24 +6144,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På levande gammal grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,22 +6166,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130142507</v>
+        <v>130142528</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6198,39 +6189,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468050</v>
+        <v>467664</v>
       </c>
       <c r="R53" t="n">
-        <v>7055309</v>
+        <v>7054936</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6267,7 +6264,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
+          <t>400 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6276,6 +6273,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6297,7 +6295,7 @@
         <v>130142509</v>
       </c>
       <c r="B54" t="n">
-        <v>80317</v>
+        <v>80343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6396,10 +6394,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130142538</v>
+        <v>130142507</v>
       </c>
       <c r="B55" t="n">
-        <v>78195</v>
+        <v>57852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6407,36 +6405,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468233</v>
+        <v>468050</v>
       </c>
       <c r="R55" t="n">
-        <v>7055007</v>
+        <v>7055309</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6473,7 +6474,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6482,7 +6483,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130142579</v>
+        <v>130142578</v>
       </c>
       <c r="B56" t="n">
-        <v>79183</v>
+        <v>78221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6512,43 +6512,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467640</v>
+        <v>467794</v>
       </c>
       <c r="R56" t="n">
-        <v>7054887</v>
+        <v>7054821</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6585,7 +6576,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1000 ex på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6612,10 +6603,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130142578</v>
+        <v>130142579</v>
       </c>
       <c r="B57" t="n">
-        <v>78195</v>
+        <v>79209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6623,34 +6614,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467794</v>
+        <v>467640</v>
       </c>
       <c r="R57" t="n">
-        <v>7054821</v>
+        <v>7054887</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1000 ex på gammal gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6717,7 +6717,7 @@
         <v>130142499</v>
       </c>
       <c r="B58" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>130142577</v>
       </c>
       <c r="B59" t="n">
-        <v>78195</v>
+        <v>78221</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130142511</v>
+        <v>130142508</v>
       </c>
       <c r="B60" t="n">
-        <v>80324</v>
+        <v>80343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6929,21 +6929,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467765</v>
+        <v>467673</v>
       </c>
       <c r="R60" t="n">
-        <v>7055022</v>
+        <v>7054942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7020,10 +7020,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130142508</v>
+        <v>130142511</v>
       </c>
       <c r="B61" t="n">
-        <v>80317</v>
+        <v>80350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7031,21 +7031,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467673</v>
+        <v>467765</v>
       </c>
       <c r="R61" t="n">
-        <v>7054942</v>
+        <v>7055022</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7122,10 +7122,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130142517</v>
+        <v>130142576</v>
       </c>
       <c r="B62" t="n">
-        <v>57007</v>
+        <v>57852</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7133,16 +7133,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7150,9 +7150,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7161,10 +7162,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468271</v>
+        <v>467637</v>
       </c>
       <c r="R62" t="n">
-        <v>7054976</v>
+        <v>7054889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7201,7 +7202,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>1 ex i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7216,12 +7217,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7231,7 +7232,7 @@
         <v>130142530</v>
       </c>
       <c r="B63" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7345,7 +7346,7 @@
         <v>130142542</v>
       </c>
       <c r="B64" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7459,7 +7460,7 @@
         <v>130142549</v>
       </c>
       <c r="B65" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7562,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130142576</v>
+        <v>130142517</v>
       </c>
       <c r="B66" t="n">
-        <v>57826</v>
+        <v>57033</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7573,16 +7574,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7590,10 +7591,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467637</v>
+        <v>468271</v>
       </c>
       <c r="R66" t="n">
-        <v>7054889</v>
+        <v>7054976</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>1 ex i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7657,22 +7657,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130130452</v>
+        <v>130142544</v>
       </c>
       <c r="B67" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7698,16 +7698,18 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468256</v>
+        <v>468267</v>
       </c>
       <c r="R67" t="n">
-        <v>7055180</v>
+        <v>7055127</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7737,24 +7739,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ca 50-100 bålar per gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7763,28 +7755,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130142544</v>
+        <v>130130452</v>
       </c>
       <c r="B68" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7810,18 +7803,16 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468267</v>
+        <v>468256</v>
       </c>
       <c r="R68" t="n">
-        <v>7055127</v>
+        <v>7055180</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,14 +7842,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ca 50-100 bålar per gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7867,19 +7868,18 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130142540</v>
+        <v>130142510</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>80315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,36 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468101</v>
+        <v>467764</v>
       </c>
       <c r="R6" t="n">
-        <v>7054854</v>
+        <v>7055038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1188,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142526</v>
+        <v>130142540</v>
       </c>
       <c r="B7" t="n">
         <v>79209</v>
@@ -1246,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468039</v>
+        <v>468101</v>
       </c>
       <c r="R7" t="n">
-        <v>7055284</v>
+        <v>7054854</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1283,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142510</v>
+        <v>130142500</v>
       </c>
       <c r="B8" t="n">
-        <v>80315</v>
+        <v>91721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467764</v>
+        <v>468254</v>
       </c>
       <c r="R8" t="n">
-        <v>7055038</v>
+        <v>7054950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,45 +1413,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130142500</v>
+        <v>130142526</v>
       </c>
       <c r="B9" t="n">
-        <v>91721</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468254</v>
+        <v>468039</v>
       </c>
       <c r="R9" t="n">
-        <v>7054950</v>
+        <v>7055284</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1490,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,6 +1499,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -3083,45 +3083,47 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142581</v>
+        <v>130142531</v>
       </c>
       <c r="B24" t="n">
-        <v>92180</v>
+        <v>78221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467806</v>
+        <v>467929</v>
       </c>
       <c r="R24" t="n">
-        <v>7054984</v>
+        <v>7055015</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3158,7 +3160,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,50 +3169,51 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130142514</v>
+        <v>130142581</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>92180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468321</v>
+        <v>467806</v>
       </c>
       <c r="R25" t="n">
-        <v>7055166</v>
+        <v>7054984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,7 +3263,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,12 +3278,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3392,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130142531</v>
+        <v>130142514</v>
       </c>
       <c r="B27" t="n">
-        <v>78221</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,36 +3406,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467929</v>
+        <v>468321</v>
       </c>
       <c r="R27" t="n">
-        <v>7055015</v>
+        <v>7055166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,7 +3470,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3478,7 +3479,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130130447</v>
+        <v>130142521</v>
       </c>
       <c r="B31" t="n">
         <v>79209</v>
@@ -3836,17 +3836,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467870</v>
+        <v>468185</v>
       </c>
       <c r="R31" t="n">
-        <v>7054963</v>
+        <v>7054913</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3876,24 +3885,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3908,19 +3907,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130142533</v>
+        <v>130130447</v>
       </c>
       <c r="B32" t="n">
         <v>79209</v>
@@ -3949,18 +3948,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468252</v>
+        <v>467870</v>
       </c>
       <c r="R32" t="n">
-        <v>7055255</v>
+        <v>7054963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,14 +3987,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,26 +4013,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130142535</v>
+        <v>130142533</v>
       </c>
       <c r="B33" t="n">
         <v>79209</v>
@@ -4053,16 +4059,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4071,10 +4068,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467691</v>
+        <v>468252</v>
       </c>
       <c r="R33" t="n">
-        <v>7054987</v>
+        <v>7055255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4111,7 +4108,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>200 bålar på gammal levande gran med kådlöpa</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,7 +4136,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130142521</v>
+        <v>130142535</v>
       </c>
       <c r="B34" t="n">
         <v>79209</v>
@@ -4169,7 +4166,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4177,16 +4174,18 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468185</v>
+        <v>467691</v>
       </c>
       <c r="R34" t="n">
-        <v>7054913</v>
+        <v>7054987</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4223,7 +4222,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>200 bålar på gammal levande gran med kådlöpa</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4232,6 +4231,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130142578</v>
+        <v>130142579</v>
       </c>
       <c r="B56" t="n">
-        <v>78221</v>
+        <v>79209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6512,34 +6512,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467794</v>
+        <v>467640</v>
       </c>
       <c r="R56" t="n">
-        <v>7054821</v>
+        <v>7054887</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6576,7 +6585,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1000 ex på gammal gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6603,10 +6612,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130142579</v>
+        <v>130142578</v>
       </c>
       <c r="B57" t="n">
-        <v>79209</v>
+        <v>78221</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6614,43 +6623,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467640</v>
+        <v>467794</v>
       </c>
       <c r="R57" t="n">
-        <v>7054887</v>
+        <v>7054821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>1000 ex på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130142527</v>
+        <v>130142506</v>
       </c>
       <c r="B2" t="n">
         <v>79209</v>
@@ -703,28 +703,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468067</v>
+        <v>468050</v>
       </c>
       <c r="R2" t="n">
-        <v>7055001</v>
+        <v>7055309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -891,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130142506</v>
+        <v>130142527</v>
       </c>
       <c r="B4" t="n">
         <v>79209</v>
@@ -919,17 +907,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468050</v>
+        <v>468067</v>
       </c>
       <c r="R4" t="n">
-        <v>7055309</v>
+        <v>7055001</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>100 bålar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130142510</v>
+        <v>130142500</v>
       </c>
       <c r="B6" t="n">
-        <v>80315</v>
+        <v>91722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467764</v>
+        <v>468254</v>
       </c>
       <c r="R6" t="n">
-        <v>7055038</v>
+        <v>7054950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142540</v>
+        <v>130142510</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>80315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,36 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468101</v>
+        <v>467764</v>
       </c>
       <c r="R7" t="n">
-        <v>7054854</v>
+        <v>7055038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1281,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1290,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,45 +1308,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142500</v>
+        <v>130142540</v>
       </c>
       <c r="B8" t="n">
-        <v>91721</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468254</v>
+        <v>468101</v>
       </c>
       <c r="R8" t="n">
-        <v>7054950</v>
+        <v>7054854</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1385,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,6 +1394,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1874,47 +1874,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130142539</v>
+        <v>130130446</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>92476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468233</v>
+        <v>467827</v>
       </c>
       <c r="R13" t="n">
-        <v>7055007</v>
+        <v>7054966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,14 +1945,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Torraka av gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,15 +1975,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1982,7 +2008,7 @@
         <v>130130445</v>
       </c>
       <c r="B14" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130142513</v>
+        <v>130142539</v>
       </c>
       <c r="B15" t="n">
-        <v>83187</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,34 +2124,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468321</v>
+        <v>468233</v>
       </c>
       <c r="R15" t="n">
-        <v>7055166</v>
+        <v>7055007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2190,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,6 +2199,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2189,48 +2218,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130130446</v>
+        <v>130142513</v>
       </c>
       <c r="B16" t="n">
-        <v>92475</v>
+        <v>83188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467827</v>
+        <v>468321</v>
       </c>
       <c r="R16" t="n">
-        <v>7054966</v>
+        <v>7055166</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,24 +2286,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Torraka av gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,44 +2302,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130142512</v>
+        <v>130142573</v>
       </c>
       <c r="B17" t="n">
-        <v>78221</v>
+        <v>91758</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467732</v>
+        <v>467742</v>
       </c>
       <c r="R17" t="n">
-        <v>7054900</v>
+        <v>7054804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,22 +2410,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130142573</v>
+        <v>130142548</v>
       </c>
       <c r="B18" t="n">
-        <v>91757</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,34 +2433,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467742</v>
+        <v>467726</v>
       </c>
       <c r="R18" t="n">
-        <v>7054804</v>
+        <v>7055026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,25 +2508,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130142548</v>
+        <v>130142536</v>
       </c>
       <c r="B19" t="n">
         <v>79209</v>
@@ -2552,7 +2555,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2561,10 +2573,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467726</v>
+        <v>468265</v>
       </c>
       <c r="R19" t="n">
-        <v>7055026</v>
+        <v>7055202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2613,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,7 +2753,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130142536</v>
+        <v>130142541</v>
       </c>
       <c r="B21" t="n">
         <v>79209</v>
@@ -2787,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468265</v>
+        <v>468161</v>
       </c>
       <c r="R21" t="n">
-        <v>7055202</v>
+        <v>7054893</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,7 +2839,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,7 +2867,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130142541</v>
+        <v>130142545</v>
       </c>
       <c r="B22" t="n">
         <v>79209</v>
@@ -2885,7 +2897,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2901,10 +2913,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468161</v>
+        <v>468004</v>
       </c>
       <c r="R22" t="n">
-        <v>7054893</v>
+        <v>7055356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,7 +2953,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>75 bålar på gammal grov gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2969,10 +2981,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130142545</v>
+        <v>130142512</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>78221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2980,45 +2992,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468004</v>
+        <v>467732</v>
       </c>
       <c r="R23" t="n">
-        <v>7055356</v>
+        <v>7054900</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3055,7 +3056,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>75 bålar på gammal grov gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,7 +3065,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142531</v>
+        <v>130142514</v>
       </c>
       <c r="B24" t="n">
-        <v>78221</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,36 +3094,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467929</v>
+        <v>468321</v>
       </c>
       <c r="R24" t="n">
-        <v>7055015</v>
+        <v>7055166</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3158,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,7 +3167,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3188,45 +3185,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130142581</v>
+        <v>130142524</v>
       </c>
       <c r="B25" t="n">
-        <v>92180</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467806</v>
+        <v>468176</v>
       </c>
       <c r="R25" t="n">
-        <v>7054984</v>
+        <v>7055315</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3262,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3272,28 +3271,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130142524</v>
+        <v>130142531</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>78221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468176</v>
+        <v>467929</v>
       </c>
       <c r="R26" t="n">
-        <v>7055315</v>
+        <v>7055015</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130142514</v>
+        <v>130142581</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>92181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468321</v>
+        <v>467806</v>
       </c>
       <c r="R27" t="n">
-        <v>7055166</v>
+        <v>7054984</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,22 +3485,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130142575</v>
+        <v>130142574</v>
       </c>
       <c r="B28" t="n">
-        <v>57852</v>
+        <v>91758</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,39 +3508,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467789</v>
+        <v>467620</v>
       </c>
       <c r="R28" t="n">
-        <v>7054982</v>
+        <v>7054890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,7 +3572,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre Ringhack</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130142574</v>
+        <v>130142575</v>
       </c>
       <c r="B29" t="n">
-        <v>91757</v>
+        <v>57852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,34 +3610,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467620</v>
+        <v>467789</v>
       </c>
       <c r="R29" t="n">
-        <v>7054890</v>
+        <v>7054982</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Äldre Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3808,7 +3808,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130142521</v>
+        <v>130142535</v>
       </c>
       <c r="B31" t="n">
         <v>79209</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3846,16 +3846,18 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468185</v>
+        <v>467691</v>
       </c>
       <c r="R31" t="n">
-        <v>7054913</v>
+        <v>7054987</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3894,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>200 bålar på gammal levande gran med kådlöpa</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3901,6 +3903,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4136,7 +4139,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130142535</v>
+        <v>130142521</v>
       </c>
       <c r="B34" t="n">
         <v>79209</v>
@@ -4166,7 +4169,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4174,18 +4177,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467691</v>
+        <v>468185</v>
       </c>
       <c r="R34" t="n">
-        <v>7054987</v>
+        <v>7054913</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4222,7 +4223,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>200 bålar på gammal levande gran med kådlöpa</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,7 +4232,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>130142520</v>
       </c>
       <c r="B35" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130142515</v>
+        <v>130142532</v>
       </c>
       <c r="B36" t="n">
-        <v>78221</v>
+        <v>79209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,34 +4359,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>468321</v>
+        <v>467929</v>
       </c>
       <c r="R36" t="n">
-        <v>7055166</v>
+        <v>7055015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4423,7 +4434,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>50 bålar på gammal levande gran, även liten svartspik</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4432,6 +4443,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4450,10 +4462,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130142572</v>
+        <v>130130451</v>
       </c>
       <c r="B37" t="n">
-        <v>83187</v>
+        <v>57852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4461,34 +4473,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467699</v>
+        <v>467987</v>
       </c>
       <c r="R37" t="n">
-        <v>7054917</v>
+        <v>7055415</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4518,14 +4538,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4536,26 +4566,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130130451</v>
+        <v>130142572</v>
       </c>
       <c r="B38" t="n">
-        <v>57852</v>
+        <v>83188</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,42 +4608,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467987</v>
+        <v>467699</v>
       </c>
       <c r="R38" t="n">
-        <v>7055415</v>
+        <v>7054917</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4628,24 +4665,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4656,41 +4683,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130142532</v>
+        <v>130142515</v>
       </c>
       <c r="B39" t="n">
-        <v>79209</v>
+        <v>78221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4698,45 +4710,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467929</v>
+        <v>468321</v>
       </c>
       <c r="R39" t="n">
-        <v>7055015</v>
+        <v>7055166</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4773,7 +4774,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran, även liten svartspik</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4782,7 +4783,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>130142519</v>
       </c>
       <c r="B40" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130142580</v>
+        <v>130130448</v>
       </c>
       <c r="B41" t="n">
-        <v>83053</v>
+        <v>79209</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,34 +4910,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467784</v>
+        <v>468041</v>
       </c>
       <c r="R41" t="n">
-        <v>7054832</v>
+        <v>7054996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,14 +4967,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På två närliggande granar</t>
+          <t>Rikligare, på gran, 100-200 bålar per gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4989,19 +4999,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130130448</v>
+        <v>130142523</v>
       </c>
       <c r="B42" t="n">
         <v>79209</v>
@@ -5032,14 +5042,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468041</v>
+        <v>467732</v>
       </c>
       <c r="R42" t="n">
-        <v>7054996</v>
+        <v>7054972</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5069,24 +5079,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligare, på gran, 100-200 bålar per gran</t>
+          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5101,19 +5101,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130142523</v>
+        <v>130142529</v>
       </c>
       <c r="B43" t="n">
         <v>79209</v>
@@ -5142,16 +5142,18 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467732</v>
+        <v>468113</v>
       </c>
       <c r="R43" t="n">
-        <v>7054972</v>
+        <v>7055367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5188,7 +5190,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5197,6 +5199,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5215,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130142529</v>
+        <v>130142580</v>
       </c>
       <c r="B44" t="n">
-        <v>79209</v>
+        <v>83054</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5226,36 +5229,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468113</v>
+        <v>467784</v>
       </c>
       <c r="R44" t="n">
-        <v>7055367</v>
+        <v>7054832</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,7 +5293,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På två närliggande granar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,67 +5302,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130130444</v>
+        <v>130142501</v>
       </c>
       <c r="B45" t="n">
-        <v>79209</v>
+        <v>91722</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467755</v>
+        <v>467935</v>
       </c>
       <c r="R45" t="n">
-        <v>7054925</v>
+        <v>7055019</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5391,24 +5388,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
+          <t>På klen död gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5417,64 +5404,66 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130142501</v>
+        <v>130130444</v>
       </c>
       <c r="B46" t="n">
-        <v>91721</v>
+        <v>79209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467935</v>
+        <v>467755</v>
       </c>
       <c r="R46" t="n">
-        <v>7055019</v>
+        <v>7054925</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,14 +5493,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På klen död gran</t>
+          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,18 +5519,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5652,47 +5652,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130142538</v>
+        <v>130142509</v>
       </c>
       <c r="B48" t="n">
-        <v>78221</v>
+        <v>80343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468233</v>
+        <v>467764</v>
       </c>
       <c r="R48" t="n">
-        <v>7055007</v>
+        <v>7055038</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5729,7 +5727,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5738,7 +5736,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5757,10 +5754,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130142534</v>
+        <v>130142507</v>
       </c>
       <c r="B49" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5768,36 +5765,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467764</v>
+        <v>468050</v>
       </c>
       <c r="R49" t="n">
-        <v>7054808</v>
+        <v>7055309</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På 200-årig gran i gammal granskog</t>
+          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5843,7 +5843,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5862,10 +5861,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130130453</v>
+        <v>130142538</v>
       </c>
       <c r="B50" t="n">
-        <v>79209</v>
+        <v>78221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,34 +5872,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468109</v>
+        <v>468233</v>
       </c>
       <c r="R50" t="n">
-        <v>7054902</v>
+        <v>7055007</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5930,24 +5931,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,25 +5947,26 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130142518</v>
+        <v>130142504</v>
       </c>
       <c r="B51" t="n">
         <v>79209</v>
@@ -6009,10 +6001,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468111</v>
+        <v>468112</v>
       </c>
       <c r="R51" t="n">
-        <v>7055166</v>
+        <v>7055457</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6049,7 +6041,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>På levande gammal grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6076,7 +6068,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130142504</v>
+        <v>130130453</v>
       </c>
       <c r="B52" t="n">
         <v>79209</v>
@@ -6107,14 +6099,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468112</v>
+        <v>468109</v>
       </c>
       <c r="R52" t="n">
-        <v>7055457</v>
+        <v>7054902</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6144,14 +6136,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På levande gammal grov gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6166,19 +6168,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130142528</v>
+        <v>130142534</v>
       </c>
       <c r="B53" t="n">
         <v>79209</v>
@@ -6206,16 +6208,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6224,10 +6217,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467664</v>
+        <v>467764</v>
       </c>
       <c r="R53" t="n">
-        <v>7054936</v>
+        <v>7054808</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6264,7 +6257,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>400 bålar på gammal levande gran i gammal granskog</t>
+          <t>På 200-årig gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6292,32 +6285,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130142509</v>
+        <v>130142518</v>
       </c>
       <c r="B54" t="n">
-        <v>80343</v>
+        <v>79209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6327,10 +6320,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467764</v>
+        <v>468111</v>
       </c>
       <c r="R54" t="n">
-        <v>7055038</v>
+        <v>7055166</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6367,7 +6360,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6394,10 +6387,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130142507</v>
+        <v>130142528</v>
       </c>
       <c r="B55" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6405,39 +6398,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468050</v>
+        <v>467664</v>
       </c>
       <c r="R55" t="n">
-        <v>7055309</v>
+        <v>7054936</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6474,7 +6473,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
+          <t>400 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6483,6 +6482,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130142579</v>
+        <v>130142578</v>
       </c>
       <c r="B56" t="n">
-        <v>79209</v>
+        <v>78221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6512,43 +6512,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467640</v>
+        <v>467794</v>
       </c>
       <c r="R56" t="n">
-        <v>7054887</v>
+        <v>7054821</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6585,7 +6576,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1000 ex på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6612,10 +6603,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130142578</v>
+        <v>130142579</v>
       </c>
       <c r="B57" t="n">
-        <v>78221</v>
+        <v>79209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6623,34 +6614,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467794</v>
+        <v>467640</v>
       </c>
       <c r="R57" t="n">
-        <v>7054821</v>
+        <v>7054887</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1000 ex på gammal gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6918,45 +6918,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130142508</v>
+        <v>130142517</v>
       </c>
       <c r="B60" t="n">
-        <v>80343</v>
+        <v>57033</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467673</v>
+        <v>468271</v>
       </c>
       <c r="R60" t="n">
-        <v>7054942</v>
+        <v>7054976</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6993,7 +6997,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>1 ex i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7020,45 +7024,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130142511</v>
+        <v>130142549</v>
       </c>
       <c r="B61" t="n">
-        <v>80350</v>
+        <v>79209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467765</v>
+        <v>467791</v>
       </c>
       <c r="R61" t="n">
-        <v>7055022</v>
+        <v>7054826</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7095,7 +7102,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7104,6 +7111,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7122,50 +7130,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130142576</v>
+        <v>130142511</v>
       </c>
       <c r="B62" t="n">
-        <v>57852</v>
+        <v>80350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467637</v>
+        <v>467765</v>
       </c>
       <c r="R62" t="n">
-        <v>7054889</v>
+        <v>7055022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7202,7 +7205,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7217,12 +7220,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7457,10 +7460,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130142549</v>
+        <v>130142576</v>
       </c>
       <c r="B65" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,37 +7471,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467791</v>
+        <v>467637</v>
       </c>
       <c r="R65" t="n">
-        <v>7054826</v>
+        <v>7054889</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7535,7 +7540,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7544,68 +7549,63 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130142517</v>
+        <v>130142508</v>
       </c>
       <c r="B66" t="n">
-        <v>57033</v>
+        <v>80343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468271</v>
+        <v>467673</v>
       </c>
       <c r="R66" t="n">
-        <v>7054976</v>
+        <v>7054942</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>1 ex i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7669,7 +7669,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130142544</v>
+        <v>130130452</v>
       </c>
       <c r="B67" t="n">
         <v>79209</v>
@@ -7698,18 +7698,16 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468267</v>
+        <v>468256</v>
       </c>
       <c r="R67" t="n">
-        <v>7055127</v>
+        <v>7055180</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7739,14 +7737,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ca 50-100 bålar per gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7755,26 +7763,25 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130130452</v>
+        <v>130142544</v>
       </c>
       <c r="B68" t="n">
         <v>79209</v>
@@ -7803,16 +7810,18 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468256</v>
+        <v>468267</v>
       </c>
       <c r="R68" t="n">
-        <v>7055180</v>
+        <v>7055127</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,24 +7851,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ca 50-100 bålar per gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7868,18 +7867,19 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130142506</v>
+        <v>130142573</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468050</v>
+        <v>467742</v>
       </c>
       <c r="R2" t="n">
-        <v>7055309</v>
+        <v>7054804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130142502</v>
+        <v>130142574</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468068</v>
+        <v>467620</v>
       </c>
       <c r="R3" t="n">
-        <v>7055228</v>
+        <v>7054890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130142527</v>
+        <v>130142580</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,45 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468067</v>
+        <v>467784</v>
       </c>
       <c r="R4" t="n">
-        <v>7055001</v>
+        <v>7054832</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran</t>
+          <t>På två närliggande granar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,29 +963,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130142522</v>
+        <v>130142510</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,43 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468134</v>
+        <v>467764</v>
       </c>
       <c r="R5" t="n">
-        <v>7054850</v>
+        <v>7055038</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130142500</v>
+        <v>130130446</v>
       </c>
       <c r="B6" t="n">
-        <v>91722</v>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468254</v>
+        <v>467827</v>
       </c>
       <c r="R6" t="n">
-        <v>7054950</v>
+        <v>7054966</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,14 +1154,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>Torraka av gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,50 +1180,66 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130142510</v>
+        <v>130142581</v>
       </c>
       <c r="B7" t="n">
-        <v>80315</v>
+        <v>92333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467764</v>
+        <v>467806</v>
       </c>
       <c r="R7" t="n">
-        <v>7055038</v>
+        <v>7054984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1289,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,59 +1304,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130142540</v>
+        <v>130142500</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468101</v>
+        <v>468254</v>
       </c>
       <c r="R8" t="n">
-        <v>7054854</v>
+        <v>7054950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,7 +1391,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1400,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1413,47 +1418,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130142526</v>
+        <v>130142501</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468039</v>
+        <v>467935</v>
       </c>
       <c r="R9" t="n">
-        <v>7055284</v>
+        <v>7055019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1493,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På klen död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,7 +1502,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1518,14 +1520,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130142537</v>
+        <v>130130444</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1546,28 +1548,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467722</v>
+        <v>467755</v>
       </c>
       <c r="R10" t="n">
-        <v>7054932</v>
+        <v>7054925</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,14 +1591,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran i gammal granskog</t>
+          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,62 +1624,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130142505</v>
+        <v>130130447</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468112</v>
+        <v>467870</v>
       </c>
       <c r="R11" t="n">
-        <v>7055457</v>
+        <v>7054963</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,14 +1704,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,65 +1736,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130130450</v>
+        <v>130130448</v>
       </c>
       <c r="B12" t="n">
-        <v>57852</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468089</v>
+        <v>468041</v>
       </c>
       <c r="R12" t="n">
-        <v>7055291</v>
+        <v>7054996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1818,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1827,12 +1828,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran med brösthöjdsdiameter 40 cm. Minst 3 ringar.</t>
+          <t>Rikligare, på gran, 100-200 bålar per gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,21 +1844,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1874,48 +1860,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130130446</v>
+        <v>130130449</v>
       </c>
       <c r="B13" t="n">
-        <v>92476</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467827</v>
+        <v>468106</v>
       </c>
       <c r="R13" t="n">
-        <v>7054966</v>
+        <v>7055256</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,12 +1940,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Torraka av gran</t>
+          <t>200 bålar per gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,24 +1954,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2005,30 +1972,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130130445</v>
+        <v>130130452</v>
       </c>
       <c r="B14" t="n">
-        <v>91778</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2036,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467790</v>
+        <v>468256</v>
       </c>
       <c r="R14" t="n">
-        <v>7054972</v>
+        <v>7055180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,7 +2042,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,12 +2052,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Högstubbe, gran, med födosök från hackspett</t>
+          <t>Ca 50-100 bålar per gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,14 +2084,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130142539</v>
+        <v>130130453</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2142,18 +2113,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468233</v>
+        <v>468109</v>
       </c>
       <c r="R15" t="n">
-        <v>7055007</v>
+        <v>7054902</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,14 +2152,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,51 +2178,50 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130142513</v>
+        <v>130142499</v>
       </c>
       <c r="B16" t="n">
-        <v>83188</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2253,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468321</v>
+        <v>468254</v>
       </c>
       <c r="R16" t="n">
-        <v>7055166</v>
+        <v>7054950</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2271,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,32 +2298,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130142573</v>
+        <v>130142502</v>
       </c>
       <c r="B17" t="n">
-        <v>91758</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2355,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467742</v>
+        <v>468068</v>
       </c>
       <c r="R17" t="n">
-        <v>7054804</v>
+        <v>7055228</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2373,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,26 +2388,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130142548</v>
+        <v>130142504</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2451,18 +2429,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467726</v>
+        <v>468112</v>
       </c>
       <c r="R18" t="n">
-        <v>7055026</v>
+        <v>7055457</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,7 +2475,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På levande gammal grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,7 +2484,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,14 +2502,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130142536</v>
+        <v>130142506</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2555,28 +2530,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468265</v>
+        <v>468050</v>
       </c>
       <c r="R19" t="n">
-        <v>7055202</v>
+        <v>7055309</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,7 +2577,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2622,7 +2586,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2641,14 +2604,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130130449</v>
+        <v>130142514</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2672,14 +2635,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468106</v>
+        <v>468321</v>
       </c>
       <c r="R20" t="n">
-        <v>7055256</v>
+        <v>7055166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,24 +2672,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>200 bålar per gran</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,26 +2694,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130142541</v>
+        <v>130142518</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2781,28 +2734,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468161</v>
+        <v>468111</v>
       </c>
       <c r="R21" t="n">
-        <v>7054893</v>
+        <v>7055166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,7 +2781,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>på gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,7 +2790,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2867,14 +2808,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130142545</v>
+        <v>130142521</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2897,7 +2838,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2905,18 +2846,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468004</v>
+        <v>468185</v>
       </c>
       <c r="R22" t="n">
-        <v>7055356</v>
+        <v>7054913</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2953,7 +2892,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>75 bålar på gammal grov gran</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,7 +2901,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2981,45 +2919,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130142512</v>
+        <v>130142522</v>
       </c>
       <c r="B23" t="n">
-        <v>78221</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467732</v>
+        <v>468134</v>
       </c>
       <c r="R23" t="n">
-        <v>7054900</v>
+        <v>7054850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,7 +3003,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
+          <t>100 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3083,14 +3030,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130142514</v>
+        <v>130142523</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3118,10 +3065,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468321</v>
+        <v>467732</v>
       </c>
       <c r="R24" t="n">
-        <v>7055166</v>
+        <v>7054972</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3158,7 +3105,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,11 +3135,11 @@
         <v>130142524</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3290,35 +3237,44 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130142531</v>
+        <v>130142525</v>
       </c>
       <c r="B26" t="n">
-        <v>78221</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3327,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467929</v>
+        <v>467757</v>
       </c>
       <c r="R26" t="n">
-        <v>7055015</v>
+        <v>7054850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3323,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på gammal levande gran</t>
+          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,45 +3351,47 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130142581</v>
+        <v>130142526</v>
       </c>
       <c r="B27" t="n">
-        <v>92181</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467806</v>
+        <v>468039</v>
       </c>
       <c r="R27" t="n">
-        <v>7054984</v>
+        <v>7055284</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3428,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,63 +3437,75 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130142574</v>
+        <v>130142527</v>
       </c>
       <c r="B28" t="n">
-        <v>91758</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467620</v>
+        <v>468067</v>
       </c>
       <c r="R28" t="n">
-        <v>7054890</v>
+        <v>7055001</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3572,7 +3542,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>100 bålar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3581,68 +3551,75 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130142575</v>
+        <v>130142528</v>
       </c>
       <c r="B29" t="n">
-        <v>57852</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467789</v>
+        <v>467664</v>
       </c>
       <c r="R29" t="n">
-        <v>7054982</v>
+        <v>7054936</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,7 +3656,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre Ringhack</t>
+          <t>400 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,63 +3665,66 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130142516</v>
+        <v>130142529</v>
       </c>
       <c r="B30" t="n">
-        <v>80274</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468102</v>
+        <v>468113</v>
       </c>
       <c r="R30" t="n">
-        <v>7055100</v>
+        <v>7055367</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3761,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3790,6 +3770,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3808,14 +3789,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130142535</v>
+        <v>130142530</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3838,7 +3819,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3854,10 +3835,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467691</v>
+        <v>468034</v>
       </c>
       <c r="R31" t="n">
-        <v>7054987</v>
+        <v>7055454</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,7 +3875,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>200 bålar på gammal levande gran med kådlöpa</t>
+          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,14 +3903,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130130447</v>
+        <v>130142532</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3950,17 +3931,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467870</v>
+        <v>467929</v>
       </c>
       <c r="R32" t="n">
-        <v>7054963</v>
+        <v>7055015</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,24 +3982,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>50 bålar på gammal levande gran, även liten svartspik</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4016,18 +3998,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4037,11 +4020,11 @@
         <v>130142533</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4139,14 +4122,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130142521</v>
+        <v>130142534</v>
       </c>
       <c r="B34" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4167,26 +4150,19 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468185</v>
+        <v>467764</v>
       </c>
       <c r="R34" t="n">
-        <v>7054913</v>
+        <v>7054808</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4223,7 +4199,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran i gammal granskog</t>
+          <t>På 200-årig gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4232,6 +4208,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4250,41 +4227,56 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130142520</v>
+        <v>130142535</v>
       </c>
       <c r="B35" t="n">
-        <v>91778</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467714</v>
+        <v>467691</v>
       </c>
       <c r="R35" t="n">
-        <v>7054901</v>
+        <v>7054987</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4321,7 +4313,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal död gran (20 cm dbh, 150-200 år i gammal granskog</t>
+          <t>200 bålar på gammal levande gran med kådlöpa</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4330,6 +4322,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4348,14 +4341,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130142532</v>
+        <v>130142536</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4394,10 +4387,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467929</v>
+        <v>468265</v>
       </c>
       <c r="R36" t="n">
-        <v>7055015</v>
+        <v>7055202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4434,7 +4427,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran, även liten svartspik</t>
+          <t>50 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4462,53 +4455,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130130451</v>
+        <v>130142537</v>
       </c>
       <c r="B37" t="n">
-        <v>57852</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467987</v>
+        <v>467722</v>
       </c>
       <c r="R37" t="n">
-        <v>7055415</v>
+        <v>7054932</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4538,24 +4534,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
+          <t>100 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4564,78 +4550,66 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130142572</v>
+        <v>130142539</v>
       </c>
       <c r="B38" t="n">
-        <v>83188</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467699</v>
+        <v>468233</v>
       </c>
       <c r="R38" t="n">
-        <v>7054917</v>
+        <v>7055007</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,7 +4646,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4681,63 +4655,66 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130142515</v>
+        <v>130142540</v>
       </c>
       <c r="B39" t="n">
-        <v>78221</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468321</v>
+        <v>468101</v>
       </c>
       <c r="R39" t="n">
-        <v>7055166</v>
+        <v>7054854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4774,7 +4751,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4783,6 +4760,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4801,41 +4779,56 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130142519</v>
+        <v>130142541</v>
       </c>
       <c r="B40" t="n">
-        <v>91778</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468111</v>
+        <v>468161</v>
       </c>
       <c r="R40" t="n">
-        <v>7055166</v>
+        <v>7054893</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4872,7 +4865,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>50 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4881,6 +4874,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4899,14 +4893,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130130448</v>
+        <v>130142542</v>
       </c>
       <c r="B41" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4927,17 +4921,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468041</v>
+        <v>467980</v>
       </c>
       <c r="R41" t="n">
-        <v>7054996</v>
+        <v>7055026</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,24 +4972,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligare, på gran, 100-200 bålar per gran</t>
+          <t>100 bålar på gammal levande gran (8 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4993,32 +4988,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130142523</v>
+        <v>130142544</v>
       </c>
       <c r="B42" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5040,16 +5036,18 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467732</v>
+        <v>468267</v>
       </c>
       <c r="R42" t="n">
-        <v>7054972</v>
+        <v>7055127</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5086,7 +5084,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död gammal gran i gammal granskog, kanten av körväg</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5095,6 +5093,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5113,14 +5112,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130142529</v>
+        <v>130142545</v>
       </c>
       <c r="B43" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5141,7 +5140,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5150,10 +5158,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468113</v>
+        <v>468004</v>
       </c>
       <c r="R43" t="n">
-        <v>7055367</v>
+        <v>7055356</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,7 +5198,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>75 bålar på gammal grov gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5218,45 +5226,47 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130142580</v>
+        <v>130142548</v>
       </c>
       <c r="B44" t="n">
-        <v>83054</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467784</v>
+        <v>467726</v>
       </c>
       <c r="R44" t="n">
-        <v>7054832</v>
+        <v>7055026</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5303,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På två närliggande granar</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,63 +5312,67 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130142501</v>
+        <v>130142549</v>
       </c>
       <c r="B45" t="n">
-        <v>91722</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467935</v>
+        <v>467791</v>
       </c>
       <c r="R45" t="n">
-        <v>7055019</v>
+        <v>7054826</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5395,7 +5409,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På klen död gran</t>
+          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5404,6 +5418,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5422,14 +5437,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130130444</v>
+        <v>130142579</v>
       </c>
       <c r="B46" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5450,20 +5465,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Forsmyrarna, Jmt</t>
+          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467755</v>
+        <v>467640</v>
       </c>
       <c r="R46" t="n">
-        <v>7054925</v>
+        <v>7054887</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5493,24 +5514,14 @@
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran, rikligt, några hundra bålar. Apotecie</t>
+          <t>1000 ex på gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5519,29 +5530,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130142525</v>
+        <v>130142513</v>
       </c>
       <c r="B47" t="n">
-        <v>79209</v>
+        <v>83307</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5549,45 +5559,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467757</v>
+        <v>468321</v>
       </c>
       <c r="R47" t="n">
-        <v>7054850</v>
+        <v>7055166</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5624,7 +5623,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>300 bålar på gammal levande gran 30 cm dbh, i ca 200 år gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5633,7 +5632,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5652,32 +5650,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130142509</v>
+        <v>130142572</v>
       </c>
       <c r="B48" t="n">
-        <v>80343</v>
+        <v>83307</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5687,10 +5685,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467764</v>
+        <v>467699</v>
       </c>
       <c r="R48" t="n">
-        <v>7055038</v>
+        <v>7054917</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5725,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5742,62 +5740,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130142507</v>
+        <v>130142508</v>
       </c>
       <c r="B49" t="n">
-        <v>57852</v>
+        <v>80461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468050</v>
+        <v>467673</v>
       </c>
       <c r="R49" t="n">
-        <v>7055309</v>
+        <v>7054942</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5827,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5861,47 +5854,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130142538</v>
+        <v>130142509</v>
       </c>
       <c r="B50" t="n">
-        <v>78221</v>
+        <v>80461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468233</v>
+        <v>467764</v>
       </c>
       <c r="R50" t="n">
-        <v>7055007</v>
+        <v>7055038</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5938,7 +5929,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5947,7 +5938,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5966,32 +5956,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130142504</v>
+        <v>130142511</v>
       </c>
       <c r="B51" t="n">
-        <v>79209</v>
+        <v>80468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6001,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468112</v>
+        <v>467765</v>
       </c>
       <c r="R51" t="n">
-        <v>7055457</v>
+        <v>7055022</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6041,7 +6031,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På levande gammal grov gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130130453</v>
+        <v>130130450</v>
       </c>
       <c r="B52" t="n">
-        <v>79209</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6079,34 +6069,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468109</v>
+        <v>468089</v>
       </c>
       <c r="R52" t="n">
-        <v>7054902</v>
+        <v>7055291</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6138,7 +6136,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6148,12 +6146,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Färska ringhack, gran med brösthöjdsdiameter 40 cm. Minst 3 ringar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6164,6 +6162,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6180,10 +6193,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130142534</v>
+        <v>130130451</v>
       </c>
       <c r="B53" t="n">
-        <v>79209</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6191,36 +6204,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
+          <t>Forsmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467764</v>
+        <v>467987</v>
       </c>
       <c r="R53" t="n">
-        <v>7054808</v>
+        <v>7055415</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6250,14 +6269,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På 200-årig gran i gammal granskog</t>
+          <t>Gran med mycket stort antal ringhack, 50 ringar. Mycket rinning efter sav kvar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6266,29 +6295,43 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130142518</v>
+        <v>130142505</v>
       </c>
       <c r="B54" t="n">
-        <v>79209</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6296,34 +6339,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468111</v>
+        <v>468112</v>
       </c>
       <c r="R54" t="n">
-        <v>7055166</v>
+        <v>7055457</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6360,7 +6408,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>Gamla ringhack på gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6387,10 +6435,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130142528</v>
+        <v>130142507</v>
       </c>
       <c r="B55" t="n">
-        <v>79209</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6398,45 +6446,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467664</v>
+        <v>468050</v>
       </c>
       <c r="R55" t="n">
-        <v>7054936</v>
+        <v>7055309</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6473,7 +6515,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>400 bålar på gammal levande gran i gammal granskog</t>
+          <t>Gamla ringhack vid basen av gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6482,7 +6524,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6501,10 +6542,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130142578</v>
+        <v>130142575</v>
       </c>
       <c r="B56" t="n">
-        <v>78221</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6512,34 +6553,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467794</v>
+        <v>467789</v>
       </c>
       <c r="R56" t="n">
-        <v>7054821</v>
+        <v>7054982</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6576,7 +6622,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Äldre Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6603,10 +6649,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130142579</v>
+        <v>130142576</v>
       </c>
       <c r="B57" t="n">
-        <v>79209</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6614,31 +6660,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6647,10 +6689,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467640</v>
+        <v>467637</v>
       </c>
       <c r="R57" t="n">
-        <v>7054887</v>
+        <v>7054889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6729,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>1000 ex på gammal gran</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6714,45 +6756,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130142499</v>
+        <v>130142517</v>
       </c>
       <c r="B58" t="n">
-        <v>79209</v>
+        <v>57132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468254</v>
+        <v>468271</v>
       </c>
       <c r="R58" t="n">
-        <v>7054950</v>
+        <v>7054976</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6789,7 +6835,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>1 ex i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6816,10 +6862,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130142577</v>
+        <v>130142512</v>
       </c>
       <c r="B59" t="n">
-        <v>78221</v>
+        <v>78339</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6851,10 +6897,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467937</v>
+        <v>467732</v>
       </c>
       <c r="R59" t="n">
-        <v>7054881</v>
+        <v>7054900</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6891,7 +6937,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6906,22 +6952,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130142517</v>
+        <v>130142515</v>
       </c>
       <c r="B60" t="n">
-        <v>57033</v>
+        <v>78339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6929,38 +6975,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468271</v>
+        <v>468321</v>
       </c>
       <c r="R60" t="n">
-        <v>7054976</v>
+        <v>7055166</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6997,7 +7039,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>1 ex i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7024,10 +7066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130142549</v>
+        <v>130142531</v>
       </c>
       <c r="B61" t="n">
-        <v>79209</v>
+        <v>78339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7035,25 +7077,24 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -7062,10 +7103,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467791</v>
+        <v>467929</v>
       </c>
       <c r="R61" t="n">
-        <v>7054826</v>
+        <v>7055015</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7102,7 +7143,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På 200-årig gran (20 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7130,45 +7171,47 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130142511</v>
+        <v>130142538</v>
       </c>
       <c r="B62" t="n">
-        <v>80350</v>
+        <v>78339</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467765</v>
+        <v>468233</v>
       </c>
       <c r="R62" t="n">
-        <v>7055022</v>
+        <v>7055007</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7205,7 +7248,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,6 +7257,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7232,10 +7276,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130142530</v>
+        <v>130142577</v>
       </c>
       <c r="B63" t="n">
-        <v>79209</v>
+        <v>78339</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7243,45 +7287,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468034</v>
+        <v>467937</v>
       </c>
       <c r="R63" t="n">
-        <v>7055454</v>
+        <v>7054881</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7318,7 +7351,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>50 bålar på gammal levande gran (ca 150-200 år, 30 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7327,29 +7360,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130142542</v>
+        <v>130142578</v>
       </c>
       <c r="B64" t="n">
-        <v>79209</v>
+        <v>78339</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7357,45 +7389,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467980</v>
+        <v>467794</v>
       </c>
       <c r="R64" t="n">
-        <v>7055026</v>
+        <v>7054821</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7432,7 +7453,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>100 bålar på gammal levande gran (8 cm dbh) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7441,69 +7462,63 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130142576</v>
+        <v>130142516</v>
       </c>
       <c r="B65" t="n">
-        <v>57852</v>
+        <v>80392</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467637</v>
+        <v>468102</v>
       </c>
       <c r="R65" t="n">
-        <v>7054889</v>
+        <v>7055100</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7540,7 +7555,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7555,334 +7570,15 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>130142508</v>
-      </c>
-      <c r="B66" t="n">
-        <v>80343</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>467673</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7054942</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gammal rönn i gammal granskog</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>130130452</v>
-      </c>
-      <c r="B67" t="n">
-        <v>79209</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Forsmyrarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>468256</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7055180</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ca 50-100 bålar per gran</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Elin Albrechtsson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Elin Albrechtsson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>130142544</v>
-      </c>
-      <c r="B68" t="n">
-        <v>79209</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Skog mellan Forsmyrarna och väg 340 mellan Landön och Lillholmsjö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>468267</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7055127</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57211-2025 artfynd.xlsx
+++ b/artfynd/A 57211-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142574</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142580</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142510</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130446</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142581</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142501</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130447</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130448</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1969,6 +2029,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130449</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130453</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142499</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2285,6 +2360,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142502</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,6 +2467,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142504</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2489,6 +2574,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +2681,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142518</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2702,6 +2797,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142521</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2813,6 +2913,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142522</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2915,6 +3020,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142523</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3020,6 +3130,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142524</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3134,6 +3249,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142525</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3239,6 +3359,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142526</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3353,6 +3478,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142527</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3467,6 +3597,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142528</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3572,6 +3707,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142529</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3686,6 +3826,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142530</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3800,6 +3945,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142532</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3905,6 +4055,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142533</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4010,6 +4165,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142534</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4124,6 +4284,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142535</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4238,6 +4403,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142537</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4343,6 +4513,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142539</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4448,6 +4623,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142540</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4562,6 +4742,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142541</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4676,6 +4861,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142542</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4790,6 +4980,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142545</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4895,6 +5090,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142548</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5001,6 +5201,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142549</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5112,6 +5317,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142579</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5214,6 +5424,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142572</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5316,6 +5531,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142508</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5418,6 +5638,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142509</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5520,6 +5745,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142511</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5655,6 +5885,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130450</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5790,6 +6025,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130451</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5897,6 +6137,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142505</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6004,6 +6249,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142507</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6111,6 +6361,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142575</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6218,6 +6473,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142576</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6320,6 +6580,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142512</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6425,6 +6690,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142531</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6530,6 +6800,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142538</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6632,6 +6907,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142577</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6734,6 +7014,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142578</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6836,6 +7121,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142516</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6948,6 +7238,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130452</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7050,6 +7345,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142514</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7164,6 +7464,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142536</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7269,6 +7574,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142544</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7371,6 +7681,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142513</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7477,6 +7792,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142517</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7579,8 +7899,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142515</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>